--- a/processing26/results_all_SHIP.xlsx
+++ b/processing26/results_all_SHIP.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,15 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="41">
   <si>
     <t>fname</t>
   </si>
   <si>
-    <t>20260408a_arrWork.c10.nc</t>
-  </si>
-  <si>
-    <t>20260408b_arrWork.c10.nc</t>
+    <t>20260408a_arr.c10.nc</t>
+  </si>
+  <si>
+    <t>20260408b_arr.c10.nc</t>
+  </si>
+  <si>
+    <t>20260624_arr.c10.nc</t>
+  </si>
+  <si>
+    <t>20260626_arr.c10.nc</t>
   </si>
   <si>
     <t>means</t>
@@ -106,6 +113,30 @@
   </si>
   <si>
     <t>CIhi_8</t>
+  </si>
+  <si>
+    <t>Clow_1</t>
+  </si>
+  <si>
+    <t>Clow_2</t>
+  </si>
+  <si>
+    <t>Clow_3</t>
+  </si>
+  <si>
+    <t>Clow_4</t>
+  </si>
+  <si>
+    <t>Clow_5</t>
+  </si>
+  <si>
+    <t>Clow_6</t>
+  </si>
+  <si>
+    <t>Clow_7</t>
+  </si>
+  <si>
+    <t>Clow_8</t>
   </si>
 </sst>
 </file>
@@ -151,35 +182,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AH20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="true"/>
+    <col min="1" max="1" width="19.7109375" customWidth="true"/>
     <col min="2" max="2" width="8.85546875" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.42578125" customWidth="true"/>
     <col min="5" max="5" width="16.42578125" customWidth="true"/>
-    <col min="6" max="6" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13.7109375" customWidth="true"/>
     <col min="7" max="7" width="15.42578125" customWidth="true"/>
-    <col min="8" max="8" width="13.7109375" customWidth="true"/>
-    <col min="9" max="9" width="14.7109375" customWidth="true"/>
-    <col min="10" max="10" width="13.42578125" customWidth="true"/>
-    <col min="11" max="11" width="14.7109375" customWidth="true"/>
+    <col min="8" max="8" width="12.7109375" customWidth="true"/>
+    <col min="9" max="9" width="15.7109375" customWidth="true"/>
+    <col min="10" max="10" width="14.42578125" customWidth="true"/>
+    <col min="11" max="11" width="15.42578125" customWidth="true"/>
     <col min="12" max="12" width="15.7109375" customWidth="true"/>
     <col min="13" max="13" width="16.42578125" customWidth="true"/>
     <col min="14" max="14" width="12.7109375" customWidth="true"/>
-    <col min="15" max="15" width="15.42578125" customWidth="true"/>
-    <col min="16" max="16" width="13.7109375" customWidth="true"/>
-    <col min="17" max="17" width="16.42578125" customWidth="true"/>
-    <col min="18" max="18" width="12.42578125" customWidth="true"/>
+    <col min="15" max="15" width="16.42578125" customWidth="true"/>
+    <col min="16" max="16" width="12.7109375" customWidth="true"/>
+    <col min="17" max="17" width="15.7109375" customWidth="true"/>
+    <col min="18" max="18" width="14.42578125" customWidth="true"/>
     <col min="19" max="19" width="14.7109375" customWidth="true"/>
     <col min="20" max="20" width="16.42578125" customWidth="true"/>
     <col min="21" max="21" width="16.42578125" customWidth="true"/>
-    <col min="22" max="22" width="12.7109375" customWidth="true"/>
-    <col min="23" max="23" width="15.5703125" customWidth="true"/>
-    <col min="24" max="24" width="13.7109375" customWidth="true"/>
+    <col min="22" max="22" width="13.7109375" customWidth="true"/>
+    <col min="23" max="23" width="15.42578125" customWidth="true"/>
+    <col min="24" max="24" width="12.7109375" customWidth="true"/>
     <col min="25" max="25" width="14.7109375" customWidth="true"/>
-    <col min="26" max="26" width="13.42578125" customWidth="true"/>
+    <col min="26" max="26" width="14.42578125" customWidth="true"/>
+    <col min="27" max="27" width="7.5703125" customWidth="true"/>
+    <col min="28" max="28" width="7.5703125" customWidth="true"/>
+    <col min="29" max="29" width="7.5703125" customWidth="true"/>
+    <col min="30" max="30" width="7.5703125" customWidth="true"/>
+    <col min="31" max="31" width="7.5703125" customWidth="true"/>
+    <col min="32" max="32" width="7.5703125" customWidth="true"/>
+    <col min="33" max="33" width="7.5703125" customWidth="true"/>
+    <col min="34" max="34" width="7.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -187,79 +226,103 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y1" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Z1" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH1" s="0" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -267,769 +330,1561 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C2" s="0">
-        <v>0.017453292499609536</v>
+        <v>0.017453292502978959</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.0026985599028262388</v>
+        <v>-0.0034611299605504342</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.0019766542948771726</v>
+        <v>-0.0019821042137898211</v>
       </c>
       <c r="F2" s="0">
-        <v>0.78175133532792263</v>
+        <v>0.77237965826706434</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.025608895073956833</v>
+        <v>-0.027644601995395049</v>
       </c>
       <c r="H2" s="0">
-        <v>0.81238248072608554</v>
+        <v>0.78746537500178015</v>
       </c>
       <c r="I2" s="0">
-        <v>0.0037944263105793258</v>
+        <v>0.0033310384230048162</v>
       </c>
       <c r="J2" s="0">
-        <v>-5.0447613541844589</v>
+        <v>-0.72128198500394469</v>
       </c>
       <c r="K2" s="0">
-        <v>0.013948657427951604</v>
+        <v>0.013796148848991607</v>
       </c>
       <c r="L2" s="0">
-        <v>-0.002937886313870779</v>
+        <v>-0.0037102004329563265</v>
       </c>
       <c r="M2" s="0">
-        <v>-0.0022132046668036729</v>
+        <v>-0.0022282979875034858</v>
       </c>
       <c r="N2" s="0">
-        <v>0.77594639633752582</v>
+        <v>0.76641247531415146</v>
       </c>
       <c r="O2" s="0">
-        <v>-0.02632552834749775</v>
+        <v>-0.028393229403472275</v>
       </c>
       <c r="P2" s="0">
-        <v>0.79889966504245724</v>
+        <v>0.77364200633468794</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.0032158874131785497</v>
+        <v>0.0027348992022662231</v>
       </c>
       <c r="R2" s="0">
-        <v>-5.0586332295676835</v>
+        <v>-0.73688281300293135</v>
       </c>
       <c r="S2" s="0">
-        <v>0.020957927571267469</v>
+        <v>0.021110436156966311</v>
       </c>
       <c r="T2" s="0">
-        <v>-0.0024592334917816986</v>
+        <v>-0.0032120594881445419</v>
       </c>
       <c r="U2" s="0">
-        <v>-0.0017401039229506721</v>
+        <v>-0.0017359104400761565</v>
       </c>
       <c r="V2" s="0">
-        <v>0.78755627431831943</v>
+        <v>0.77834684121997722</v>
       </c>
       <c r="W2" s="0">
-        <v>-0.024892261800415917</v>
+        <v>-0.026895974587317823</v>
       </c>
       <c r="X2" s="0">
-        <v>0.82586529640971384</v>
+        <v>0.80128874366887237</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.0043729652079801014</v>
+        <v>0.0039271776437434097</v>
       </c>
       <c r="Z2" s="0">
-        <v>-5.0308894788012344</v>
-      </c>
+        <v>-0.70568115700495804</v>
+      </c>
+      <c r="AA2" s="0"/>
+      <c r="AB2" s="0"/>
+      <c r="AC2" s="0"/>
+      <c r="AD2" s="0"/>
+      <c r="AE2" s="0"/>
+      <c r="AF2" s="0"/>
+      <c r="AG2" s="0"/>
+      <c r="AH2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C3" s="0">
-        <v>0.017453292508344428</v>
+        <v>0.017453292519369598</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.0010153984761985151</v>
+        <v>-0.0010552797105670853</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.00036679992823318515</v>
+        <v>-0.00026763475663411657</v>
       </c>
       <c r="F3" s="0">
-        <v>0.78080740231115497</v>
+        <v>0.76791062309293812</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.023290048305809094</v>
+        <v>-0.023613754741642085</v>
       </c>
       <c r="H3" s="0">
-        <v>0.7226788561580435</v>
+        <v>0.71064813462452581</v>
       </c>
       <c r="I3" s="0">
-        <v>0.0035199279787753771</v>
+        <v>0.0033605797579225657</v>
       </c>
       <c r="J3" s="0">
-        <v>-4.9877606897787459</v>
+        <v>-0.43738127592719483</v>
       </c>
       <c r="K3" s="0">
-        <v>0.013309613869268355</v>
+        <v>0.013471613638286029</v>
       </c>
       <c r="L3" s="0">
-        <v>-0.0012859500781924609</v>
+        <v>-0.0013151529350747262</v>
       </c>
       <c r="M3" s="0">
-        <v>-0.00063204872814472623</v>
+        <v>-0.00052240888763405678</v>
       </c>
       <c r="N3" s="0">
-        <v>0.77403660364455318</v>
+        <v>0.76151732289495566</v>
       </c>
       <c r="O3" s="0">
-        <v>-0.024098353661426746</v>
+        <v>-0.024391685354071595</v>
       </c>
       <c r="P3" s="0">
-        <v>0.70801822472161013</v>
+        <v>0.69676925251800226</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.0028606109457724807</v>
+        <v>0.0027277059651523387</v>
       </c>
       <c r="R3" s="0">
-        <v>-5.0038083718310569</v>
+        <v>-0.45375562132209091</v>
       </c>
       <c r="S3" s="0">
-        <v>0.021596971147420499</v>
+        <v>0.021434971400453168</v>
       </c>
       <c r="T3" s="0">
-        <v>-0.00074484687420456948</v>
+        <v>-0.00079540648605944445</v>
       </c>
       <c r="U3" s="0">
-        <v>-0.00010155112832164407</v>
+        <v>-1.2860625634176365e-05</v>
       </c>
       <c r="V3" s="0">
-        <v>0.78757820097775677</v>
+        <v>0.77430392329092057</v>
       </c>
       <c r="W3" s="0">
-        <v>-0.022481742950191442</v>
+        <v>-0.022835824129212576</v>
       </c>
       <c r="X3" s="0">
-        <v>0.73733948759447687</v>
+        <v>0.72452701673104936</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.0041792450117782735</v>
+        <v>0.0039934535506927927</v>
       </c>
       <c r="Z3" s="0">
-        <v>-4.9717130077264349</v>
-      </c>
+        <v>-0.42100693053229876</v>
+      </c>
+      <c r="AA3" s="0"/>
+      <c r="AB3" s="0"/>
+      <c r="AC3" s="0"/>
+      <c r="AD3" s="0"/>
+      <c r="AE3" s="0"/>
+      <c r="AF3" s="0"/>
+      <c r="AG3" s="0"/>
+      <c r="AH3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="0">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C4" s="0">
-        <v>0.0074225801067767088</v>
+        <v>0.0084731399021472607</v>
       </c>
       <c r="D4" s="0">
-        <v>0.017453292396844899</v>
+        <v>0.017453292477796267</v>
       </c>
       <c r="E4" s="0">
-        <v>0.028132462918619674</v>
+        <v>0.022539289649647031</v>
       </c>
       <c r="F4" s="0">
-        <v>0.5310416645178867</v>
+        <v>0.54509889441655623</v>
       </c>
       <c r="G4" s="0">
-        <v>0.03412047096963991</v>
+        <v>0.032089908843038535</v>
       </c>
       <c r="H4" s="0">
-        <v>0.74414362558688052</v>
+        <v>0.73611451831627095</v>
       </c>
       <c r="I4" s="0">
-        <v>0.0023350299198718534</v>
+        <v>0.0030491763661513989</v>
       </c>
       <c r="J4" s="0">
-        <v>-14.387223433739205</v>
+        <v>-10.181827394116441</v>
       </c>
       <c r="K4" s="0">
-        <v>0.0020384262988475555</v>
+        <v>0.0033789176186130214</v>
       </c>
       <c r="L4" s="0">
-        <v>0.016101168850975817</v>
+        <v>0.016159176819595184</v>
       </c>
       <c r="M4" s="0">
-        <v>0.022823649646153223</v>
+        <v>0.017387801339523504</v>
       </c>
       <c r="N4" s="0">
-        <v>0.4391231883963278</v>
+        <v>0.4572564282302416</v>
       </c>
       <c r="O4" s="0">
-        <v>0.025988826939071091</v>
+        <v>0.024188770747897874</v>
       </c>
       <c r="P4" s="0">
-        <v>0.73370494903434946</v>
+        <v>0.72676880588190551</v>
       </c>
       <c r="Q4" s="0">
-        <v>-0.00031081458619803756</v>
+        <v>0.00049681708166833235</v>
       </c>
       <c r="R4" s="0">
-        <v>-15.811108410896829</v>
+        <v>-11.520870913439333</v>
       </c>
       <c r="S4" s="0">
-        <v>0.012806733914705862</v>
+        <v>0.013567362185681501</v>
       </c>
       <c r="T4" s="0">
-        <v>0.018805415942713982</v>
+        <v>0.018747408135997349</v>
       </c>
       <c r="U4" s="0">
-        <v>0.033441276191086125</v>
+        <v>0.027690777959770558</v>
       </c>
       <c r="V4" s="0">
-        <v>0.6229601406394456</v>
+        <v>0.63294136060287087</v>
       </c>
       <c r="W4" s="0">
-        <v>0.042252115000208729</v>
+        <v>0.039991046938179196</v>
       </c>
       <c r="X4" s="0">
-        <v>0.75458230213941158</v>
+        <v>0.74546023075063639</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.0049808744259417443</v>
+        <v>0.0056015356506344659</v>
       </c>
       <c r="Z4" s="0">
-        <v>-12.963338456581582</v>
-      </c>
+        <v>-8.8427838747935486</v>
+      </c>
+      <c r="AA4" s="0"/>
+      <c r="AB4" s="0"/>
+      <c r="AC4" s="0"/>
+      <c r="AD4" s="0"/>
+      <c r="AE4" s="0"/>
+      <c r="AF4" s="0"/>
+      <c r="AG4" s="0"/>
+      <c r="AH4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="0">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C5" s="0">
-        <v>0.0024574239044129103</v>
+        <v>0.0020760125369999388</v>
       </c>
       <c r="D5" s="0">
-        <v>0.016611986288103856</v>
+        <v>0.017453292395101832</v>
       </c>
       <c r="E5" s="0">
-        <v>-0.0062397161306523416</v>
+        <v>-0.010534755969131908</v>
       </c>
       <c r="F5" s="0">
-        <v>0.77444441278373577</v>
+        <v>0.71601033481974108</v>
       </c>
       <c r="G5" s="0">
-        <v>0.015316914253864703</v>
+        <v>0.020293064053763316</v>
       </c>
       <c r="H5" s="0">
-        <v>0.66985107680334466</v>
+        <v>0.64826370881182449</v>
       </c>
       <c r="I5" s="0">
-        <v>0.0039339530002159943</v>
+        <v>0.0020217192593385723</v>
       </c>
       <c r="J5" s="0">
-        <v>-8.323403116191022</v>
+        <v>-6.0344887499139137</v>
       </c>
       <c r="K5" s="0">
-        <v>-0.010010182531739169</v>
+        <v>-0.010923255052409184</v>
       </c>
       <c r="L5" s="0">
-        <v>0.013478033025195478</v>
+        <v>0.014221822232093182</v>
       </c>
       <c r="M5" s="0">
-        <v>-0.01684820417153499</v>
+        <v>-0.021513602891010855</v>
       </c>
       <c r="N5" s="0">
-        <v>0.56138776085268405</v>
+        <v>0.50012679614525035</v>
       </c>
       <c r="O5" s="0">
-        <v>-0.0015716451308502109</v>
+        <v>0.002826923483536161</v>
       </c>
       <c r="P5" s="0">
-        <v>0.65172048647254666</v>
+        <v>0.62979469040800495</v>
       </c>
       <c r="Q5" s="0">
-        <v>-0.0031228722395326355</v>
+        <v>-0.0053753642063215073</v>
       </c>
       <c r="R5" s="0">
-        <v>-10.681910422505348</v>
+        <v>-8.4735217400053848</v>
       </c>
       <c r="S5" s="0">
-        <v>0.014925030340564992</v>
+        <v>0.015075280126409064</v>
       </c>
       <c r="T5" s="0">
-        <v>0.019745939551012233</v>
+        <v>0.020684762558110484</v>
       </c>
       <c r="U5" s="0">
-        <v>0.0043687719102303074</v>
+        <v>0.00044409095274703693</v>
       </c>
       <c r="V5" s="0">
-        <v>0.98750106471478749</v>
+        <v>0.93189387349423181</v>
       </c>
       <c r="W5" s="0">
-        <v>0.032205473638579618</v>
+        <v>0.037759204623990475</v>
       </c>
       <c r="X5" s="0">
-        <v>0.68798166713414266</v>
+        <v>0.66673272721564403</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.010990778239964624</v>
+        <v>0.0094188027249986518</v>
       </c>
       <c r="Z5" s="0">
-        <v>-5.9648958098766958</v>
-      </c>
+        <v>-3.5954557598224422</v>
+      </c>
+      <c r="AA5" s="0"/>
+      <c r="AB5" s="0"/>
+      <c r="AC5" s="0"/>
+      <c r="AD5" s="0"/>
+      <c r="AE5" s="0"/>
+      <c r="AF5" s="0"/>
+      <c r="AG5" s="0"/>
+      <c r="AH5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="0">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C6" s="0">
-        <v>0.0174532925199078</v>
+        <v>0.017453292518585621</v>
       </c>
       <c r="D6" s="0">
-        <v>0.00050546420354583531</v>
+        <v>0.00028108066502495661</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.00076878836048285587</v>
+        <v>-0.00067526844007368369</v>
       </c>
       <c r="F6" s="0">
-        <v>0.84928672435457897</v>
+        <v>0.83672439652871278</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.019995863772198148</v>
+        <v>-0.020787395353420109</v>
       </c>
       <c r="H6" s="0">
-        <v>0.78923741827754135</v>
+        <v>0.77531522432552835</v>
       </c>
       <c r="I6" s="0">
-        <v>0.0051518154585214861</v>
+        <v>0.0049352569192693098</v>
       </c>
       <c r="J6" s="0">
-        <v>-4.9047840239160809</v>
+        <v>-0.74304790164608847</v>
       </c>
       <c r="K6" s="0">
-        <v>0.015387820649723239</v>
+        <v>0.015488725066334121</v>
       </c>
       <c r="L6" s="0">
-        <v>0.00036817955334520776</v>
+        <v>0.0001506671194881325</v>
       </c>
       <c r="M6" s="0">
-        <v>-0.00090592024694081995</v>
+        <v>-0.00080553616917807122</v>
       </c>
       <c r="N6" s="0">
-        <v>0.8449211988588653</v>
+        <v>0.83264030296755687</v>
       </c>
       <c r="O6" s="0">
-        <v>-0.020462962792295078</v>
+        <v>-0.021232489223868202</v>
       </c>
       <c r="P6" s="0">
-        <v>0.78402768187700978</v>
+        <v>0.77043494062867024</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.0047933997213672934</v>
+        <v>0.0045957430917924844</v>
       </c>
       <c r="R6" s="0">
-        <v>-4.913250030240941</v>
+        <v>-0.75174176828181683</v>
       </c>
       <c r="S6" s="0">
-        <v>0.019518764390092362</v>
+        <v>0.019417859970837122</v>
       </c>
       <c r="T6" s="0">
-        <v>0.00064274885374646291</v>
+        <v>0.00041149421056178073</v>
       </c>
       <c r="U6" s="0">
-        <v>-0.00063165647402489179</v>
+        <v>-0.00054500071096929615</v>
       </c>
       <c r="V6" s="0">
-        <v>0.85365224985029264</v>
+        <v>0.84080849008986869</v>
       </c>
       <c r="W6" s="0">
-        <v>-0.019528764752101219</v>
+        <v>-0.020342301482972017</v>
       </c>
       <c r="X6" s="0">
-        <v>0.79444715467807292</v>
+        <v>0.78019550802238646</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.0055102311956756788</v>
+        <v>0.0052747707467461352</v>
       </c>
       <c r="Z6" s="0">
-        <v>-4.8963180175912209</v>
-      </c>
+        <v>-0.73435403501036012</v>
+      </c>
+      <c r="AA6" s="0"/>
+      <c r="AB6" s="0"/>
+      <c r="AC6" s="0"/>
+      <c r="AD6" s="0"/>
+      <c r="AE6" s="0"/>
+      <c r="AF6" s="0"/>
+      <c r="AG6" s="0"/>
+      <c r="AH6" s="0"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="0">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C7" s="0">
-        <v>0.010219114202352563</v>
+        <v>0.00092386585576805468</v>
       </c>
       <c r="D7" s="0">
-        <v>0.0033061030674676533</v>
+        <v>0.0051046165257119733</v>
       </c>
       <c r="E7" s="0">
-        <v>0.012441466268947684</v>
+        <v>0.0048220727102142565</v>
       </c>
       <c r="F7" s="0">
-        <v>0.73057635736752402</v>
+        <v>0.80069108504127218</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.013226735183276247</v>
+        <v>-0.012283411447464806</v>
       </c>
       <c r="H7" s="0">
-        <v>0.80180948284600007</v>
+        <v>0.78797220646588495</v>
       </c>
       <c r="I7" s="0">
-        <v>0.012095922900977359</v>
+        <v>0.0038234430987622537</v>
       </c>
       <c r="J7" s="0">
-        <v>-0.7599836000559973</v>
+        <v>7.9858164417800808</v>
       </c>
       <c r="K7" s="0">
-        <v>0.006184681904769453</v>
+        <v>-0.0036883022907283078</v>
       </c>
       <c r="L7" s="0">
-        <v>0.0019770698138932286</v>
+        <v>0.0039214030032957026</v>
       </c>
       <c r="M7" s="0">
-        <v>0.0089131023907188488</v>
+        <v>0.00062982242928778798</v>
       </c>
       <c r="N7" s="0">
-        <v>0.65083966949436622</v>
+        <v>0.70389404058719574</v>
       </c>
       <c r="O7" s="0">
-        <v>-0.019223641523590174</v>
+        <v>-0.019466059688426247</v>
       </c>
       <c r="P7" s="0">
-        <v>0.79531077835874875</v>
+        <v>0.78008203032057777</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.0091793300134002595</v>
+        <v>0.0015025361071070915</v>
       </c>
       <c r="R7" s="0">
-        <v>-1.4353552246128529</v>
+        <v>6.5667345952727532</v>
       </c>
       <c r="S7" s="0">
-        <v>0.014253546499935673</v>
+        <v>0.0055360340022644174</v>
       </c>
       <c r="T7" s="0">
-        <v>0.0046351363210420781</v>
+        <v>0.0062878300481282439</v>
       </c>
       <c r="U7" s="0">
-        <v>0.015969830147176518</v>
+        <v>0.009014322991140725</v>
       </c>
       <c r="V7" s="0">
-        <v>0.81031304524068182</v>
+        <v>0.89748812949534862</v>
       </c>
       <c r="W7" s="0">
-        <v>-0.0072298288429623178</v>
+        <v>-0.005100763206503366</v>
       </c>
       <c r="X7" s="0">
-        <v>0.80830818733325138</v>
+        <v>0.79586238261119213</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.015012515788554458</v>
+        <v>0.0061443500904174164</v>
       </c>
       <c r="Z7" s="0">
-        <v>-0.084611975499141678</v>
-      </c>
+        <v>9.4048982882874075</v>
+      </c>
+      <c r="AA7" s="0"/>
+      <c r="AB7" s="0"/>
+      <c r="AC7" s="0"/>
+      <c r="AD7" s="0"/>
+      <c r="AE7" s="0"/>
+      <c r="AF7" s="0"/>
+      <c r="AG7" s="0"/>
+      <c r="AH7" s="0"/>
     </row>
     <row r="8">
-      <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
-      <c r="C8" s="0"/>
-      <c r="D8" s="0"/>
-      <c r="E8" s="0"/>
-      <c r="F8" s="0"/>
-      <c r="G8" s="0"/>
-      <c r="H8" s="0"/>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0"/>
-      <c r="K8" s="0"/>
-      <c r="L8" s="0"/>
-      <c r="M8" s="0"/>
-      <c r="N8" s="0"/>
-      <c r="O8" s="0"/>
-      <c r="P8" s="0"/>
-      <c r="Q8" s="0"/>
-      <c r="R8" s="0"/>
-      <c r="S8" s="0"/>
-      <c r="T8" s="0"/>
-      <c r="U8" s="0"/>
-      <c r="V8" s="0"/>
-      <c r="W8" s="0"/>
-      <c r="X8" s="0"/>
-      <c r="Y8" s="0"/>
-      <c r="Z8" s="0"/>
+      <c r="A8" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="0">
+        <v>464</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.010885850102746248</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.0037926595520403647</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0.0085475114728210608</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0.68300634352365131</v>
+      </c>
+      <c r="G8" s="0">
+        <v>-0.01007860741944072</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0.78630232255653532</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0.011481102745694249</v>
+      </c>
+      <c r="J8" s="0">
+        <v>2.6356551618877724</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0.0067423814184362982</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0.0024362034208628503</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0.0049184844056796677</v>
+      </c>
+      <c r="N8" s="0">
+        <v>0.60314907653626426</v>
+      </c>
+      <c r="O8" s="0">
+        <v>-0.016211354299034978</v>
+      </c>
+      <c r="P8" s="0">
+        <v>0.77978262043677482</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>0.0084959625748527289</v>
+      </c>
+      <c r="R8" s="0">
+        <v>1.885667288071228</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0.015029318787056198</v>
+      </c>
+      <c r="T8" s="0">
+        <v>0.0051491156832178791</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0.012176538539962454</v>
+      </c>
+      <c r="V8" s="0">
+        <v>0.76286361051103835</v>
+      </c>
+      <c r="W8" s="0">
+        <v>-0.0039458605398464608</v>
+      </c>
+      <c r="X8" s="0">
+        <v>0.79282202467629581</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>0.01446624291653577</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>3.3856430357043168</v>
+      </c>
+      <c r="AA8" s="0"/>
+      <c r="AB8" s="0"/>
+      <c r="AC8" s="0"/>
+      <c r="AD8" s="0"/>
+      <c r="AE8" s="0"/>
+      <c r="AF8" s="0"/>
+      <c r="AG8" s="0"/>
+      <c r="AH8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="0"/>
+      <c r="B9" s="0">
+        <v>555</v>
+      </c>
       <c r="C9" s="0">
-        <v>0.012076499290233992</v>
+        <v>0.0041583967243602107</v>
       </c>
       <c r="D9" s="0">
-        <v>0.0056938145961562487</v>
+        <v>-0.0038536124723047181</v>
       </c>
       <c r="E9" s="0">
-        <v>0.0052036617455536336</v>
+        <v>-0.00061082504668464601</v>
       </c>
       <c r="F9" s="0">
-        <v>0.7413179827771339</v>
+        <v>0.71437198331333263</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.0054473595186226185</v>
+        <v>-0.02396976280794343</v>
       </c>
       <c r="H9" s="0">
-        <v>0.75668382339964924</v>
+        <v>0.77926312591219216</v>
       </c>
       <c r="I9" s="0">
-        <v>0.0051385125948235659</v>
+        <v>0.007721571079848848</v>
       </c>
       <c r="J9" s="0">
-        <v>-6.4013193696442512</v>
+        <v>-0.29717081819581048</v>
       </c>
       <c r="K9" s="0">
-        <v>0.0068098362698035056</v>
+        <v>0.0010272278156979015</v>
       </c>
       <c r="L9" s="0">
-        <v>0.004616769141891082</v>
+        <v>-0.0040295137568664968</v>
       </c>
       <c r="M9" s="0">
-        <v>0.0018562290372413106</v>
+        <v>-0.00079111116013829926</v>
       </c>
       <c r="N9" s="0">
-        <v>0.67437580293072041</v>
+        <v>0.69231914045656351</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.010948884086098143</v>
+        <v>-0.026218130294046151</v>
       </c>
       <c r="P9" s="0">
-        <v>0.74528029758445369</v>
+        <v>0.77447741555454253</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.002769256877997985</v>
+        <v>0.0072495590400039264</v>
       </c>
       <c r="R9" s="0">
-        <v>-7.1506776149424516</v>
+        <v>-0.31072595246624729</v>
       </c>
       <c r="S9" s="0">
-        <v>0.017343162310664472</v>
+        <v>0.0072895656330225194</v>
       </c>
       <c r="T9" s="0">
-        <v>0.0067708600504214145</v>
+        <v>-0.0036777111877429394</v>
       </c>
       <c r="U9" s="0">
-        <v>0.0085510944538659574</v>
+        <v>-0.00043053893323099276</v>
       </c>
       <c r="V9" s="0">
-        <v>0.80826016262354727</v>
+        <v>0.73642482617010174</v>
       </c>
       <c r="W9" s="0">
-        <v>5.4165048852908671e-05</v>
+        <v>-0.021721395321840708</v>
       </c>
       <c r="X9" s="0">
-        <v>0.76808734921484501</v>
+        <v>0.78404883626984179</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.0075077683116491463</v>
+        <v>0.0081935831196937696</v>
       </c>
       <c r="Z9" s="0">
-        <v>-5.6519611243460517</v>
-      </c>
+        <v>-0.28361568392537367</v>
+      </c>
+      <c r="AA9" s="0"/>
+      <c r="AB9" s="0"/>
+      <c r="AC9" s="0"/>
+      <c r="AD9" s="0"/>
+      <c r="AE9" s="0"/>
+      <c r="AF9" s="0"/>
+      <c r="AG9" s="0"/>
+      <c r="AH9" s="0"/>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="0"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="0">
+        <v>555</v>
+      </c>
       <c r="C10" s="0">
-        <v>0.0063932021768487255</v>
+        <v>0.01533660770618357</v>
       </c>
       <c r="D10" s="0">
-        <v>0.0090061915054244317</v>
+        <v>0.00050946661500639128</v>
       </c>
       <c r="E10" s="0">
-        <v>0.012863310435025577</v>
+        <v>0.00064017647079376184</v>
       </c>
       <c r="F10" s="0">
-        <v>0.10980017514879864</v>
+        <v>0.74337825860198059</v>
       </c>
       <c r="G10" s="0">
-        <v>0.024469552491617776</v>
+        <v>-0.017122200596019068</v>
       </c>
       <c r="H10" s="0">
-        <v>0.054866970661143349</v>
+        <v>0.78226757012630011</v>
       </c>
       <c r="I10" s="0">
-        <v>0.0035254105621579592</v>
+        <v>0.0066009561898845194</v>
       </c>
       <c r="J10" s="0">
-        <v>4.5906808807985886</v>
+        <v>-0.03695832521044834</v>
       </c>
       <c r="K10" s="0">
-        <v>0.0097248331190615614</v>
+        <v>0.013091287876697274</v>
       </c>
       <c r="L10" s="0">
-        <v>0.0080913147703958379</v>
+        <v>0.00039605053593986546</v>
       </c>
       <c r="M10" s="0">
-        <v>0.013188398657585832</v>
+        <v>0.00052831487452158828</v>
       </c>
       <c r="N10" s="0">
-        <v>0.15362202484751336</v>
+        <v>0.7398213710030066</v>
       </c>
       <c r="O10" s="0">
-        <v>0.02010306518585608</v>
+        <v>-0.017607494169486558</v>
       </c>
       <c r="P10" s="0">
-        <v>0.058575309450324763</v>
+        <v>0.77620673278297625</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.0042331558443891616</v>
+        <v>0.0061781320130268862</v>
       </c>
       <c r="R10" s="0">
-        <v>5.1793697723237591</v>
+        <v>-0.042785915856796662</v>
       </c>
       <c r="S10" s="0">
-        <v>0.00379122493638452</v>
+        <v>0.017581927535669867</v>
       </c>
       <c r="T10" s="0">
-        <v>0.0099697418585749081</v>
+        <v>0.00062288269407291715</v>
       </c>
       <c r="U10" s="0">
-        <v>0.013835827132944931</v>
+        <v>0.00075203806706593539</v>
       </c>
       <c r="V10" s="0">
-        <v>0.11780021185728286</v>
+        <v>0.74693514620095458</v>
       </c>
       <c r="W10" s="0">
-        <v>0.029601056375140988</v>
+        <v>-0.016636907022551578</v>
       </c>
       <c r="X10" s="0">
-        <v>0.051372334845535023</v>
+        <v>0.78832840746962396</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.0044661840076005432</v>
+        <v>0.0070237803667421526</v>
       </c>
       <c r="Z10" s="0">
-        <v>4.1465408993702804</v>
-      </c>
+        <v>-0.03113073456410002</v>
+      </c>
+      <c r="AA10" s="0"/>
+      <c r="AB10" s="0"/>
+      <c r="AC10" s="0"/>
+      <c r="AD10" s="0"/>
+      <c r="AE10" s="0"/>
+      <c r="AF10" s="0"/>
+      <c r="AG10" s="0"/>
+      <c r="AH10" s="0"/>
     </row>
     <row r="11">
-      <c r="A11" s="0"/>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
-      <c r="N11" s="0"/>
-      <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
-      <c r="S11" s="0"/>
-      <c r="T11" s="0"/>
-      <c r="U11" s="0"/>
-      <c r="V11" s="0"/>
-      <c r="W11" s="0"/>
-      <c r="X11" s="0"/>
-      <c r="Y11" s="0"/>
-      <c r="Z11" s="0"/>
+      <c r="A11" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="0">
+        <v>391</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.0043750838059252598</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0.003855096591234597</v>
+      </c>
+      <c r="E11" s="0">
+        <v>-0.034906582811064374</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0.70745813062978902</v>
+      </c>
+      <c r="G11" s="0">
+        <v>-0.0058628365542440636</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0.77684449305774583</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0.00098673745819003985</v>
+      </c>
+      <c r="J11" s="0">
+        <v>3.972782877571198</v>
+      </c>
+      <c r="K11" s="0">
+        <v>-0.0010195216857747909</v>
+      </c>
+      <c r="L11" s="0">
+        <v>0.0013962174191912932</v>
+      </c>
+      <c r="M11" s="0">
+        <v>-0.04237299684731994</v>
+      </c>
+      <c r="N11" s="0">
+        <v>0.64137178270156281</v>
+      </c>
+      <c r="O11" s="0">
+        <v>-0.013193292182913485</v>
+      </c>
+      <c r="P11" s="0">
+        <v>0.76868720017837067</v>
+      </c>
+      <c r="Q11" s="0">
+        <v>-0.0042874724337891735</v>
+      </c>
+      <c r="R11" s="0">
+        <v>2.5251110061638506</v>
+      </c>
+      <c r="S11" s="0">
+        <v>0.0097696892976253114</v>
+      </c>
+      <c r="T11" s="0">
+        <v>0.0063139757632779004</v>
+      </c>
+      <c r="U11" s="0">
+        <v>-0.027440168774808808</v>
+      </c>
+      <c r="V11" s="0">
+        <v>0.77354447855801523</v>
+      </c>
+      <c r="W11" s="0">
+        <v>0.0014676190744253581</v>
+      </c>
+      <c r="X11" s="0">
+        <v>0.785001785937121</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>0.0062609473501692541</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>5.4204547489785453</v>
+      </c>
+      <c r="AA11" s="0"/>
+      <c r="AB11" s="0"/>
+      <c r="AC11" s="0"/>
+      <c r="AD11" s="0"/>
+      <c r="AE11" s="0"/>
+      <c r="AF11" s="0"/>
+      <c r="AG11" s="0"/>
+      <c r="AH11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="0">
+        <v>464</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.017453219229896177</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0.0046725439003982528</v>
+      </c>
+      <c r="E12" s="0">
+        <v>0.0016674587423236276</v>
+      </c>
+      <c r="F12" s="0">
+        <v>0.86002224227047186</v>
+      </c>
+      <c r="G12" s="0">
+        <v>-0.019661809766329672</v>
+      </c>
+      <c r="H12" s="0">
+        <v>0.76677801824794611</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0.0053655283253346555</v>
+      </c>
+      <c r="J12" s="0">
+        <v>-0.3398236245130154</v>
+      </c>
+      <c r="K12" s="0">
+        <v>0.013711400381021288</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0.0044336680251024288</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.0014254027485168666</v>
+      </c>
+      <c r="N12" s="0">
+        <v>0.84042749564163854</v>
+      </c>
+      <c r="O12" s="0">
+        <v>-0.021768978443207986</v>
+      </c>
+      <c r="P12" s="0">
+        <v>0.76078214752986406</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>0.0046146088440916595</v>
+      </c>
+      <c r="R12" s="0">
+        <v>-0.35747011018888314</v>
+      </c>
+      <c r="S12" s="0">
+        <v>0.021195038078771066</v>
+      </c>
+      <c r="T12" s="0">
+        <v>0.0049114197756940769</v>
+      </c>
+      <c r="U12" s="0">
+        <v>0.0019095147361303886</v>
+      </c>
+      <c r="V12" s="0">
+        <v>0.87961698889930518</v>
+      </c>
+      <c r="W12" s="0">
+        <v>-0.017554641089451359</v>
+      </c>
+      <c r="X12" s="0">
+        <v>0.77277388896602817</v>
+      </c>
+      <c r="Y12" s="0">
+        <v>0.0061164478065776516</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>-0.32217713883714766</v>
+      </c>
+      <c r="AA12" s="0"/>
+      <c r="AB12" s="0"/>
+      <c r="AC12" s="0"/>
+      <c r="AD12" s="0"/>
+      <c r="AE12" s="0"/>
+      <c r="AF12" s="0"/>
+      <c r="AG12" s="0"/>
+      <c r="AH12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="0">
+        <v>464</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.0059280148711249713</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0.0020836308876135156</v>
+      </c>
+      <c r="E13" s="0">
+        <v>0.0013291485771579352</v>
+      </c>
+      <c r="F13" s="0">
+        <v>0.85615888642614568</v>
+      </c>
+      <c r="G13" s="0">
+        <v>-0.026355107390931654</v>
+      </c>
+      <c r="H13" s="0">
+        <v>0.7475882997265797</v>
+      </c>
+      <c r="I13" s="0">
+        <v>0.0014755085276827408</v>
+      </c>
+      <c r="J13" s="0">
+        <v>-0.12411931797857205</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0.0010705153513174909</v>
+      </c>
+      <c r="L13" s="0">
+        <v>0.0018580401057492753</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.0011098943575592666</v>
+      </c>
+      <c r="N13" s="0">
+        <v>0.84877983526052825</v>
+      </c>
+      <c r="O13" s="0">
+        <v>-0.027387740724083218</v>
+      </c>
+      <c r="P13" s="0">
+        <v>0.73170173774468394</v>
+      </c>
+      <c r="Q13" s="0">
+        <v>0.00051957359693336695</v>
+      </c>
+      <c r="R13" s="0">
+        <v>-0.13658723435922737</v>
+      </c>
+      <c r="S13" s="0">
+        <v>0.010785514390932453</v>
+      </c>
+      <c r="T13" s="0">
+        <v>0.002309221669477756</v>
+      </c>
+      <c r="U13" s="0">
+        <v>0.0015484027967566038</v>
+      </c>
+      <c r="V13" s="0">
+        <v>0.86353793759176312</v>
+      </c>
+      <c r="W13" s="0">
+        <v>-0.025322474057780091</v>
+      </c>
+      <c r="X13" s="0">
+        <v>0.76347486170847545</v>
+      </c>
+      <c r="Y13" s="0">
+        <v>0.0024314434584321145</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>-0.11165140159791673</v>
+      </c>
+      <c r="AA13" s="0"/>
+      <c r="AB13" s="0"/>
+      <c r="AC13" s="0"/>
+      <c r="AD13" s="0"/>
+      <c r="AE13" s="0"/>
+      <c r="AF13" s="0"/>
+      <c r="AG13" s="0"/>
+      <c r="AH13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="0">
+        <v>464</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.017453292511261598</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0.0092716172182242367</v>
+      </c>
+      <c r="E14" s="0">
+        <v>-0.00071929598988773093</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0.73677601153753103</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.0024434088381772843</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0.97111492772343766</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0.011157280617098997</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0.34457879128216779</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0.0094037815957136763</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0.0080454930148425446</v>
+      </c>
+      <c r="M14" s="0">
+        <v>-0.0019309891363610068</v>
+      </c>
+      <c r="N14" s="0">
+        <v>0.72355645056385498</v>
+      </c>
+      <c r="O14" s="0">
+        <v>-0.00036911263280190029</v>
+      </c>
+      <c r="P14" s="0">
+        <v>0.93706000171390469</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>0.0085620751209391187</v>
+      </c>
+      <c r="R14" s="0">
+        <v>0.30143529740722363</v>
+      </c>
+      <c r="S14" s="0">
+        <v>0.025502803426809519</v>
+      </c>
+      <c r="T14" s="0">
+        <v>0.010497741421605929</v>
+      </c>
+      <c r="U14" s="0">
+        <v>0.00049239715658554487</v>
+      </c>
+      <c r="V14" s="0">
+        <v>0.74999557251120708</v>
+      </c>
+      <c r="W14" s="0">
+        <v>0.0052559303091564685</v>
+      </c>
+      <c r="X14" s="0">
+        <v>1.0051698537329707</v>
+      </c>
+      <c r="Y14" s="0">
+        <v>0.013752486113258876</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>0.38772228515711194</v>
+      </c>
+      <c r="AA14" s="0"/>
+      <c r="AB14" s="0"/>
+      <c r="AC14" s="0"/>
+      <c r="AD14" s="0"/>
+      <c r="AE14" s="0"/>
+      <c r="AF14" s="0"/>
+      <c r="AG14" s="0"/>
+      <c r="AH14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="0">
+        <v>465</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.0061443380700334097</v>
+      </c>
+      <c r="D15" s="0">
+        <v>-0.017453292519425949</v>
+      </c>
+      <c r="E15" s="0">
+        <v>-0.0057788673842583691</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0.72644656961671272</v>
+      </c>
+      <c r="G15" s="0">
+        <v>-0.048635072109916085</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0.79456774951277209</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0.010664065481723634</v>
+      </c>
+      <c r="J15" s="0">
+        <v>5.258020501155233</v>
+      </c>
+      <c r="K15" s="0">
+        <v>0.0019717609762513778</v>
+      </c>
+      <c r="L15" s="0">
+        <v>-0.019926155224890791</v>
+      </c>
+      <c r="M15" s="0">
+        <v>-0.01260676452015469</v>
+      </c>
+      <c r="N15" s="0">
+        <v>0.66530948983677252</v>
+      </c>
+      <c r="O15" s="0">
+        <v>-0.056143140072090758</v>
+      </c>
+      <c r="P15" s="0">
+        <v>0.78771096690985054</v>
+      </c>
+      <c r="Q15" s="0">
+        <v>0.0057149965748189467</v>
+      </c>
+      <c r="R15" s="0">
+        <v>4.0930209428220437</v>
+      </c>
+      <c r="S15" s="0">
+        <v>0.010316915163815442</v>
+      </c>
+      <c r="T15" s="0">
+        <v>-0.014980429813961107</v>
+      </c>
+      <c r="U15" s="0">
+        <v>0.0010490297516379515</v>
+      </c>
+      <c r="V15" s="0">
+        <v>0.78758364939665293</v>
+      </c>
+      <c r="W15" s="0">
+        <v>-0.041127004147741411</v>
+      </c>
+      <c r="X15" s="0">
+        <v>0.80142453211569365</v>
+      </c>
+      <c r="Y15" s="0">
+        <v>0.015613134388628321</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>6.4230200594884224</v>
+      </c>
+      <c r="AA15" s="0"/>
+      <c r="AB15" s="0"/>
+      <c r="AC15" s="0"/>
+      <c r="AD15" s="0"/>
+      <c r="AE15" s="0"/>
+      <c r="AF15" s="0"/>
+      <c r="AG15" s="0"/>
+      <c r="AH15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
+      <c r="O16" s="0"/>
+      <c r="P16" s="0"/>
+      <c r="Q16" s="0"/>
+      <c r="R16" s="0"/>
+      <c r="S16" s="0"/>
+      <c r="T16" s="0"/>
+      <c r="U16" s="0"/>
+      <c r="V16" s="0"/>
+      <c r="W16" s="0"/>
+      <c r="X16" s="0"/>
+      <c r="Y16" s="0"/>
+      <c r="Z16" s="0"/>
+      <c r="AA16" s="0"/>
+      <c r="AB16" s="0"/>
+      <c r="AC16" s="0"/>
+      <c r="AD16" s="0"/>
+      <c r="AE16" s="0"/>
+      <c r="AF16" s="0"/>
+      <c r="AG16" s="0"/>
+      <c r="AH16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="0"/>
-      <c r="C12" s="0">
-        <v>0.017453292519911963</v>
-      </c>
-      <c r="D12" s="0">
-        <v>-0.00083166635979889175</v>
-      </c>
-      <c r="E12" s="0">
-        <v>-0.0014181212713143814</v>
-      </c>
-      <c r="F12" s="0">
-        <v>0.79844785803642393</v>
-      </c>
-      <c r="G12" s="0">
-        <v>-0.022079838041080682</v>
-      </c>
-      <c r="H12" s="0">
-        <v>0.78641411575112141</v>
-      </c>
-      <c r="I12" s="0">
-        <v>0.004832689517453745</v>
-      </c>
-      <c r="J12" s="0">
-        <v>-4.9787612205420917</v>
-      </c>
-      <c r="K12" s="0">
-        <v>0.015678641248588466</v>
-      </c>
-      <c r="L12" s="0">
-        <v>-0.00095379816614962092</v>
-      </c>
-      <c r="M12" s="0">
-        <v>-0.0015401257001548708</v>
-      </c>
-      <c r="N12" s="0">
-        <v>0.79519359114799637</v>
-      </c>
-      <c r="O12" s="0">
-        <v>-0.022457342141524818</v>
-      </c>
-      <c r="P12" s="0">
-        <v>0.78152012534727611</v>
-      </c>
-      <c r="Q12" s="0">
-        <v>0.0045285711494369042</v>
-      </c>
-      <c r="R12" s="0">
-        <v>-4.9861707886482494</v>
-      </c>
-      <c r="S12" s="0">
-        <v>0.01922794379123546</v>
-      </c>
-      <c r="T12" s="0">
-        <v>-0.00070953455344816257</v>
-      </c>
-      <c r="U12" s="0">
-        <v>-0.001296116842473892</v>
-      </c>
-      <c r="V12" s="0">
-        <v>0.80170212492485149</v>
-      </c>
-      <c r="W12" s="0">
-        <v>-0.021702333940636545</v>
-      </c>
-      <c r="X12" s="0">
-        <v>0.79130810615496672</v>
-      </c>
-      <c r="Y12" s="0">
-        <v>0.0051368078854705859</v>
-      </c>
-      <c r="Z12" s="0">
-        <v>-4.971351652435934</v>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0">
+        <v>0.010397692775527207</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0.0027609987260931571</v>
+      </c>
+      <c r="E17" s="0">
+        <v>-0.0011378340706119268</v>
+      </c>
+      <c r="F17" s="0">
+        <v>0.74760238700613557</v>
+      </c>
+      <c r="G17" s="0">
+        <v>-0.012942012746269115</v>
+      </c>
+      <c r="H17" s="0">
+        <v>0.77503611960066598</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0.0054267117321361857</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0.091482455797930226</v>
+      </c>
+      <c r="K17" s="0">
+        <v>0.0055373343970319859</v>
+      </c>
+      <c r="L17" s="0">
+        <v>0.0017169799533122943</v>
+      </c>
+      <c r="M17" s="0">
+        <v>-0.0040551419603008379</v>
+      </c>
+      <c r="N17" s="0">
+        <v>0.69832728629568164</v>
+      </c>
+      <c r="O17" s="0">
+        <v>-0.017526215161147812</v>
+      </c>
+      <c r="P17" s="0">
+        <v>0.76385003921020111</v>
+      </c>
+      <c r="Q17" s="0">
+        <v>0.0031235551837530307</v>
+      </c>
+      <c r="R17" s="0">
+        <v>-0.5294552099418296</v>
+      </c>
+      <c r="S17" s="0">
+        <v>0.015258051154022427</v>
+      </c>
+      <c r="T17" s="0">
+        <v>0.0038050174988740202</v>
+      </c>
+      <c r="U17" s="0">
+        <v>0.0017794738190769824</v>
+      </c>
+      <c r="V17" s="0">
+        <v>0.79687748771658984</v>
+      </c>
+      <c r="W17" s="0">
+        <v>-0.0083578103313904206</v>
+      </c>
+      <c r="X17" s="0">
+        <v>0.78622219999113086</v>
+      </c>
+      <c r="Y17" s="0">
+        <v>0.007729868280519343</v>
+      </c>
+      <c r="Z17" s="0">
+        <v>0.71242012153768974</v>
+      </c>
+      <c r="AA17" s="0"/>
+      <c r="AB17" s="0"/>
+      <c r="AC17" s="0"/>
+      <c r="AD17" s="0"/>
+      <c r="AE17" s="0"/>
+      <c r="AF17" s="0"/>
+      <c r="AG17" s="0"/>
+      <c r="AH17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="0"/>
+      <c r="C18" s="0">
+        <v>0.0065015674177380826</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0.0087830728879895927</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0.012276795588028256</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0.081186884086595579</v>
+      </c>
+      <c r="G18" s="0">
+        <v>0.020489494147016615</v>
+      </c>
+      <c r="H18" s="0">
+        <v>0.069006229397747781</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0.0035907861796131112</v>
+      </c>
+      <c r="J18" s="0">
+        <v>4.4351757374015817</v>
+      </c>
+      <c r="K18" s="0">
+        <v>0.0079768484677627885</v>
+      </c>
+      <c r="L18" s="0">
+        <v>0.0086030940313560952</v>
+      </c>
+      <c r="M18" s="0">
+        <v>0.013944191670417588</v>
+      </c>
+      <c r="N18" s="0">
+        <v>0.11855344276150329</v>
+      </c>
+      <c r="O18" s="0">
+        <v>0.018258947869323514</v>
+      </c>
+      <c r="P18" s="0">
+        <v>0.065870059695426128</v>
+      </c>
+      <c r="Q18" s="0">
+        <v>0.0042937489597340457</v>
+      </c>
+      <c r="R18" s="0">
+        <v>4.5747043602061517</v>
+      </c>
+      <c r="S18" s="0">
+        <v>0.0060179921608553809</v>
+      </c>
+      <c r="T18" s="0">
+        <v>0.0090793521345831942</v>
+      </c>
+      <c r="U18" s="0">
+        <v>0.011491074165993053</v>
+      </c>
+      <c r="V18" s="0">
+        <v>0.078168323331155753</v>
+      </c>
+      <c r="W18" s="0">
+        <v>0.02347924220381074</v>
+      </c>
+      <c r="X18" s="0">
+        <v>0.072866323296130436</v>
+      </c>
+      <c r="Y18" s="0">
+        <v>0.0041295299334551559</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>4.4387303276849011</v>
+      </c>
+      <c r="AA18" s="0"/>
+      <c r="AB18" s="0"/>
+      <c r="AC18" s="0"/>
+      <c r="AD18" s="0"/>
+      <c r="AE18" s="0"/>
+      <c r="AF18" s="0"/>
+      <c r="AG18" s="0"/>
+      <c r="AH18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+      <c r="C19" s="0"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
+      <c r="O19" s="0"/>
+      <c r="P19" s="0"/>
+      <c r="Q19" s="0"/>
+      <c r="R19" s="0"/>
+      <c r="S19" s="0"/>
+      <c r="T19" s="0"/>
+      <c r="U19" s="0"/>
+      <c r="V19" s="0"/>
+      <c r="W19" s="0"/>
+      <c r="X19" s="0"/>
+      <c r="Y19" s="0"/>
+      <c r="Z19" s="0"/>
+      <c r="AA19" s="0"/>
+      <c r="AB19" s="0"/>
+      <c r="AC19" s="0"/>
+      <c r="AD19" s="0"/>
+      <c r="AE19" s="0"/>
+      <c r="AF19" s="0"/>
+      <c r="AG19" s="0"/>
+      <c r="AH19" s="0"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="0"/>
+      <c r="C20" s="0">
+        <v>0.017453292513164097</v>
+      </c>
+      <c r="D20" s="0">
+        <v>-0.00057089804056733912</v>
+      </c>
+      <c r="E20" s="0">
+        <v>-0.000568744645598793</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0.7710967609274898</v>
+      </c>
+      <c r="G20" s="0">
+        <v>-0.020828066719061161</v>
+      </c>
+      <c r="H20" s="0">
+        <v>0.76781532726080359</v>
+      </c>
+      <c r="I20" s="0">
+        <v>0.0048761525870936505</v>
+      </c>
+      <c r="J20" s="0">
+        <v>-0.4746453244966028</v>
+      </c>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
+      <c r="N20" s="0"/>
+      <c r="O20" s="0"/>
+      <c r="P20" s="0"/>
+      <c r="Q20" s="0"/>
+      <c r="R20" s="0"/>
+      <c r="S20" s="0">
+        <v>0.018673228145556019</v>
+      </c>
+      <c r="T20" s="0">
+        <v>-0.00048290366678096098</v>
+      </c>
+      <c r="U20" s="0">
+        <v>-0.00048060412778311887</v>
+      </c>
+      <c r="V20" s="0">
+        <v>0.77337183458901759</v>
+      </c>
+      <c r="W20" s="0">
+        <v>-0.020544972825856166</v>
+      </c>
+      <c r="X20" s="0">
+        <v>0.77073532993273475</v>
+      </c>
+      <c r="Y20" s="0">
+        <v>0.0051028436270321165</v>
+      </c>
+      <c r="Z20" s="0">
+        <v>-0.46892554964112815</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>0.016233356880772175</v>
+      </c>
+      <c r="AB20" s="0">
+        <v>-0.00065889241435371725</v>
+      </c>
+      <c r="AC20" s="0">
+        <v>-0.00065688516341446714</v>
+      </c>
+      <c r="AD20" s="0">
+        <v>0.76882168726596201</v>
+      </c>
+      <c r="AE20" s="0">
+        <v>-0.021111160612266155</v>
+      </c>
+      <c r="AF20" s="0">
+        <v>0.76489532458887244</v>
+      </c>
+      <c r="AG20" s="0">
+        <v>0.0046494615471551846</v>
+      </c>
+      <c r="AH20" s="0">
+        <v>-0.48036509935207744</v>
       </c>
     </row>
   </sheetData>

--- a/processing26/results_all_SHIP.xlsx
+++ b/processing26/results_all_SHIP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="54" uniqueCount="42">
   <si>
     <t>fname</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>20260626_arr.c10.nc</t>
+  </si>
+  <si>
+    <t>20260831_arr.c10.nc</t>
   </si>
   <si>
     <t>means</t>
@@ -182,35 +185,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH20"/>
+  <dimension ref="A1:AH23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="true"/>
     <col min="2" max="2" width="8.85546875" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.42578125" customWidth="true"/>
+    <col min="3" max="3" width="15.42578125" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="16.42578125" customWidth="true"/>
-    <col min="6" max="6" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="12.7109375" customWidth="true"/>
     <col min="7" max="7" width="15.42578125" customWidth="true"/>
     <col min="8" max="8" width="12.7109375" customWidth="true"/>
-    <col min="9" max="9" width="15.7109375" customWidth="true"/>
-    <col min="10" max="10" width="14.42578125" customWidth="true"/>
+    <col min="9" max="9" width="16.42578125" customWidth="true"/>
+    <col min="10" max="10" width="12.7109375" customWidth="true"/>
     <col min="11" max="11" width="15.42578125" customWidth="true"/>
     <col min="12" max="12" width="15.7109375" customWidth="true"/>
     <col min="13" max="13" width="16.42578125" customWidth="true"/>
     <col min="14" max="14" width="12.7109375" customWidth="true"/>
-    <col min="15" max="15" width="16.42578125" customWidth="true"/>
+    <col min="15" max="15" width="15.42578125" customWidth="true"/>
     <col min="16" max="16" width="12.7109375" customWidth="true"/>
     <col min="17" max="17" width="15.7109375" customWidth="true"/>
-    <col min="18" max="18" width="14.42578125" customWidth="true"/>
+    <col min="18" max="18" width="13.7109375" customWidth="true"/>
     <col min="19" max="19" width="14.7109375" customWidth="true"/>
     <col min="20" max="20" width="16.42578125" customWidth="true"/>
     <col min="21" max="21" width="16.42578125" customWidth="true"/>
-    <col min="22" max="22" width="13.7109375" customWidth="true"/>
+    <col min="22" max="22" width="12.7109375" customWidth="true"/>
     <col min="23" max="23" width="15.42578125" customWidth="true"/>
     <col min="24" max="24" width="12.7109375" customWidth="true"/>
     <col min="25" max="25" width="14.7109375" customWidth="true"/>
-    <col min="26" max="26" width="14.42578125" customWidth="true"/>
+    <col min="26" max="26" width="12.42578125" customWidth="true"/>
     <col min="27" max="27" width="7.5703125" customWidth="true"/>
     <col min="28" max="28" width="7.5703125" customWidth="true"/>
     <col min="29" max="29" width="7.5703125" customWidth="true"/>
@@ -226,103 +229,103 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC1" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AD1" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE1" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF1" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AG1" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AH1" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
@@ -330,79 +333,79 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C2" s="0">
-        <v>0.017453292502978959</v>
+        <v>0.017453292503118167</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.0034611299605504342</v>
+        <v>-0.0035045775175928311</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.0019821042137898211</v>
+        <v>-0.0019269065282780632</v>
       </c>
       <c r="F2" s="0">
-        <v>0.77237965826706434</v>
+        <v>0.77182667038953667</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.027644601995395049</v>
+        <v>-0.027662504189099553</v>
       </c>
       <c r="H2" s="0">
-        <v>0.78746537500178015</v>
+        <v>0.79930779127102247</v>
       </c>
       <c r="I2" s="0">
-        <v>0.0033310384230048162</v>
+        <v>0.0033760939254961994</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.72128198500394469</v>
+        <v>-2.6897576254184825</v>
       </c>
       <c r="K2" s="0">
-        <v>0.013796148848991607</v>
+        <v>0.013959783163348203</v>
       </c>
       <c r="L2" s="0">
-        <v>-0.0037102004329563265</v>
+        <v>-0.0037429086687214893</v>
       </c>
       <c r="M2" s="0">
-        <v>-0.0022282979875034858</v>
+        <v>-0.0021627230217184327</v>
       </c>
       <c r="N2" s="0">
-        <v>0.76641247531415146</v>
+        <v>0.76612735532181941</v>
       </c>
       <c r="O2" s="0">
-        <v>-0.028393229403472275</v>
+        <v>-0.028378446426564837</v>
       </c>
       <c r="P2" s="0">
-        <v>0.77364200633468794</v>
+        <v>0.78596759786529713</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.0027348992022662231</v>
+        <v>0.0028050973743456564</v>
       </c>
       <c r="R2" s="0">
-        <v>-0.73688281300293135</v>
+        <v>-2.7034892308390353</v>
       </c>
       <c r="S2" s="0">
-        <v>0.021110436156966311</v>
+        <v>0.020946801842888132</v>
       </c>
       <c r="T2" s="0">
-        <v>-0.0032120594881445419</v>
+        <v>-0.0032662463664641728</v>
       </c>
       <c r="U2" s="0">
-        <v>-0.0017359104400761565</v>
+        <v>-0.0016910900348376934</v>
       </c>
       <c r="V2" s="0">
-        <v>0.77834684121997722</v>
+        <v>0.77752598545725393</v>
       </c>
       <c r="W2" s="0">
-        <v>-0.026895974587317823</v>
+        <v>-0.026946561951634269</v>
       </c>
       <c r="X2" s="0">
-        <v>0.80128874366887237</v>
+        <v>0.81264798467674781</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.0039271776437434097</v>
+        <v>0.0039470904766467424</v>
       </c>
       <c r="Z2" s="0">
-        <v>-0.70568115700495804</v>
+        <v>-2.6760260199979298</v>
       </c>
       <c r="AA2" s="0"/>
       <c r="AB2" s="0"/>
@@ -418,79 +421,79 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C3" s="0">
-        <v>0.017453292519369598</v>
+        <v>0.017453292508419281</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.0010552797105670853</v>
+        <v>-0.0010649163750569277</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.00026763475663411657</v>
+        <v>-0.00030878435440587535</v>
       </c>
       <c r="F3" s="0">
-        <v>0.76791062309293812</v>
+        <v>0.76827796976989438</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.023613754741642085</v>
+        <v>-0.023652277855416216</v>
       </c>
       <c r="H3" s="0">
-        <v>0.71064813462452581</v>
+        <v>0.7121597989929277</v>
       </c>
       <c r="I3" s="0">
-        <v>0.0033605797579225657</v>
+        <v>0.0033596722537983952</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.43738127592719483</v>
+        <v>-2.6057610040633295</v>
       </c>
       <c r="K3" s="0">
-        <v>0.013471613638286029</v>
+        <v>0.013406404211997286</v>
       </c>
       <c r="L3" s="0">
-        <v>-0.0013151529350747262</v>
+        <v>-0.0013287877264740199</v>
       </c>
       <c r="M3" s="0">
-        <v>-0.00052240888763405678</v>
+        <v>-0.00056755322465398513</v>
       </c>
       <c r="N3" s="0">
-        <v>0.76151732289495566</v>
+        <v>0.76177732432757927</v>
       </c>
       <c r="O3" s="0">
-        <v>-0.024391685354071595</v>
+        <v>-0.024442642799519524</v>
       </c>
       <c r="P3" s="0">
-        <v>0.69676925251800226</v>
+        <v>0.69802569549557458</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.0027277059651523387</v>
+        <v>0.0027166878714351803</v>
       </c>
       <c r="R3" s="0">
-        <v>-0.45375562132209091</v>
+        <v>-2.6213264394403773</v>
       </c>
       <c r="S3" s="0">
-        <v>0.021434971400453168</v>
+        <v>0.021500180804841278</v>
       </c>
       <c r="T3" s="0">
-        <v>-0.00079540648605944445</v>
+        <v>-0.00080104502363983554</v>
       </c>
       <c r="U3" s="0">
-        <v>-1.2860625634176365e-05</v>
+        <v>-5.001548415776557e-05</v>
       </c>
       <c r="V3" s="0">
-        <v>0.77430392329092057</v>
+        <v>0.77477861521220948</v>
       </c>
       <c r="W3" s="0">
-        <v>-0.022835824129212576</v>
+        <v>-0.022861912911312909</v>
       </c>
       <c r="X3" s="0">
-        <v>0.72452701673104936</v>
+        <v>0.72629390249028081</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.0039934535506927927</v>
+        <v>0.0040026566361616106</v>
       </c>
       <c r="Z3" s="0">
-        <v>-0.42100693053229876</v>
+        <v>-2.5901955686862816</v>
       </c>
       <c r="AA3" s="0"/>
       <c r="AB3" s="0"/>
@@ -506,79 +509,79 @@
         <v>1</v>
       </c>
       <c r="B4" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C4" s="0">
-        <v>0.0084731399021472607</v>
+        <v>0.0046501606303478551</v>
       </c>
       <c r="D4" s="0">
-        <v>0.017453292477796267</v>
+        <v>0.017453292481448529</v>
       </c>
       <c r="E4" s="0">
-        <v>0.022539289649647031</v>
+        <v>0.015199268627525471</v>
       </c>
       <c r="F4" s="0">
-        <v>0.54509889441655623</v>
+        <v>0.57059750408759324</v>
       </c>
       <c r="G4" s="0">
-        <v>0.032089908843038535</v>
+        <v>0.030017960252805207</v>
       </c>
       <c r="H4" s="0">
-        <v>0.73611451831627095</v>
+        <v>0.72796398033415599</v>
       </c>
       <c r="I4" s="0">
-        <v>0.0030491763661513989</v>
+        <v>0.00044490183158667424</v>
       </c>
       <c r="J4" s="0">
-        <v>-10.181827394116441</v>
+        <v>-14.404841049381711</v>
       </c>
       <c r="K4" s="0">
-        <v>0.0033789176186130214</v>
+        <v>-0.0013490783997223404</v>
       </c>
       <c r="L4" s="0">
-        <v>0.016159176819595184</v>
+        <v>0.015962699974907096</v>
       </c>
       <c r="M4" s="0">
-        <v>0.017387801339523504</v>
+        <v>0.0094766742049893771</v>
       </c>
       <c r="N4" s="0">
-        <v>0.4572564282302416</v>
+        <v>0.47106044093720434</v>
       </c>
       <c r="O4" s="0">
-        <v>0.024188770747897874</v>
+        <v>0.021028655682119722</v>
       </c>
       <c r="P4" s="0">
-        <v>0.72676880588190551</v>
+        <v>0.71658839807310748</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.00049681708166833235</v>
+        <v>-0.0025293531543174835</v>
       </c>
       <c r="R4" s="0">
-        <v>-11.520870913439333</v>
+        <v>-15.771476521935762</v>
       </c>
       <c r="S4" s="0">
-        <v>0.013567362185681501</v>
+        <v>0.01064939966041805</v>
       </c>
       <c r="T4" s="0">
-        <v>0.018747408135997349</v>
+        <v>0.018943884987989962</v>
       </c>
       <c r="U4" s="0">
-        <v>0.027690777959770558</v>
+        <v>0.020921863050061565</v>
       </c>
       <c r="V4" s="0">
-        <v>0.63294136060287087</v>
+        <v>0.67013456723798215</v>
       </c>
       <c r="W4" s="0">
-        <v>0.039991046938179196</v>
+        <v>0.039007264823490692</v>
       </c>
       <c r="X4" s="0">
-        <v>0.74546023075063639</v>
+        <v>0.7393395625952045</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.0056015356506344659</v>
+        <v>0.003419156817490832</v>
       </c>
       <c r="Z4" s="0">
-        <v>-8.8427838747935486</v>
+        <v>-13.038205576827659</v>
       </c>
       <c r="AA4" s="0"/>
       <c r="AB4" s="0"/>
@@ -594,79 +597,79 @@
         <v>1</v>
       </c>
       <c r="B5" s="0">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C5" s="0">
-        <v>0.0020760125369999388</v>
+        <v>-0.004546906373325668</v>
       </c>
       <c r="D5" s="0">
-        <v>0.017453292395101832</v>
+        <v>0.016834725438301036</v>
       </c>
       <c r="E5" s="0">
-        <v>-0.010534755969131908</v>
+        <v>0.01231799263419214</v>
       </c>
       <c r="F5" s="0">
-        <v>0.71601033481974108</v>
+        <v>0.66746577207515323</v>
       </c>
       <c r="G5" s="0">
-        <v>0.020293064053763316</v>
+        <v>0.022533561390315034</v>
       </c>
       <c r="H5" s="0">
-        <v>0.64826370881182449</v>
+        <v>0.67605420711769793</v>
       </c>
       <c r="I5" s="0">
-        <v>0.0020217192593385723</v>
+        <v>-0.00046149822129755419</v>
       </c>
       <c r="J5" s="0">
-        <v>-6.0344887499139137</v>
+        <v>-6.9143631350981973</v>
       </c>
       <c r="K5" s="0">
-        <v>-0.010923255052409184</v>
+        <v>-0.018942765836634266</v>
       </c>
       <c r="L5" s="0">
-        <v>0.014221822232093182</v>
+        <v>0.013317843712922325</v>
       </c>
       <c r="M5" s="0">
-        <v>-0.021513602891010855</v>
+        <v>0.00089378257010140107</v>
       </c>
       <c r="N5" s="0">
-        <v>0.50012679614525035</v>
+        <v>0.46035404090630366</v>
       </c>
       <c r="O5" s="0">
-        <v>0.002826923483536161</v>
+        <v>0.0054403881157467325</v>
       </c>
       <c r="P5" s="0">
-        <v>0.62979469040800495</v>
+        <v>0.6554619331692626</v>
       </c>
       <c r="Q5" s="0">
-        <v>-0.0053753642063215073</v>
+        <v>-0.0086659995909133709</v>
       </c>
       <c r="R5" s="0">
-        <v>-8.4735217400053848</v>
+        <v>-9.2475011278424546</v>
       </c>
       <c r="S5" s="0">
-        <v>0.015075280126409064</v>
+        <v>0.0098489530899829314</v>
       </c>
       <c r="T5" s="0">
-        <v>0.020684762558110484</v>
+        <v>0.020351607163679748</v>
       </c>
       <c r="U5" s="0">
-        <v>0.00044409095274703693</v>
+        <v>0.02374220269828288</v>
       </c>
       <c r="V5" s="0">
-        <v>0.93189387349423181</v>
+        <v>0.87457750324400285</v>
       </c>
       <c r="W5" s="0">
-        <v>0.037759204623990475</v>
+        <v>0.03962673466488334</v>
       </c>
       <c r="X5" s="0">
-        <v>0.66673272721564403</v>
+        <v>0.69664648106613325</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.0094188027249986518</v>
+        <v>0.0077430031483182622</v>
       </c>
       <c r="Z5" s="0">
-        <v>-3.5954557598224422</v>
+        <v>-4.5812251423539392</v>
       </c>
       <c r="AA5" s="0"/>
       <c r="AB5" s="0"/>
@@ -682,79 +685,79 @@
         <v>2</v>
       </c>
       <c r="B6" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C6" s="0">
-        <v>0.017453292518585621</v>
+        <v>0.017453292519912098</v>
       </c>
       <c r="D6" s="0">
-        <v>0.00028108066502495661</v>
+        <v>0.00027809164857527964</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.00067526844007368369</v>
+        <v>-0.00062881877283743409</v>
       </c>
       <c r="F6" s="0">
-        <v>0.83672439652871278</v>
+        <v>0.83679130458748941</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.020787395353420109</v>
+        <v>-0.020810227333077979</v>
       </c>
       <c r="H6" s="0">
-        <v>0.77531522432552835</v>
+        <v>0.77712407628304647</v>
       </c>
       <c r="I6" s="0">
-        <v>0.0049352569192693098</v>
+        <v>0.0049196817541785386</v>
       </c>
       <c r="J6" s="0">
-        <v>-0.74304790164608847</v>
+        <v>-2.6595821175685162</v>
       </c>
       <c r="K6" s="0">
-        <v>0.015488725066334121</v>
+        <v>0.015593127973570346</v>
       </c>
       <c r="L6" s="0">
-        <v>0.0001506671194881325</v>
+        <v>0.00015453470722375578</v>
       </c>
       <c r="M6" s="0">
-        <v>-0.00080553616917807122</v>
+        <v>-0.00075224493349274274</v>
       </c>
       <c r="N6" s="0">
-        <v>0.83264030296755687</v>
+        <v>0.83292409434541315</v>
       </c>
       <c r="O6" s="0">
-        <v>-0.021232489223868202</v>
+        <v>-0.021231938032324909</v>
       </c>
       <c r="P6" s="0">
-        <v>0.77043494062867024</v>
+        <v>0.77249302144293874</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.0045957430917924844</v>
+        <v>0.0045979205393013034</v>
       </c>
       <c r="R6" s="0">
-        <v>-0.75174176828181683</v>
+        <v>-2.6671494627768415</v>
       </c>
       <c r="S6" s="0">
-        <v>0.019417859970837122</v>
+        <v>0.019313457066253849</v>
       </c>
       <c r="T6" s="0">
-        <v>0.00041149421056178073</v>
+        <v>0.00040164858992680348</v>
       </c>
       <c r="U6" s="0">
-        <v>-0.00054500071096929615</v>
+        <v>-0.00050539261218212543</v>
       </c>
       <c r="V6" s="0">
-        <v>0.84080849008986869</v>
+        <v>0.84065851482956566</v>
       </c>
       <c r="W6" s="0">
-        <v>-0.020342301482972017</v>
+        <v>-0.020388516633831049</v>
       </c>
       <c r="X6" s="0">
-        <v>0.78019550802238646</v>
+        <v>0.7817551311231542</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.0052747707467461352</v>
+        <v>0.0052414429690557738</v>
       </c>
       <c r="Z6" s="0">
-        <v>-0.73435403501036012</v>
+        <v>-2.6520147723601908</v>
       </c>
       <c r="AA6" s="0"/>
       <c r="AB6" s="0"/>
@@ -770,79 +773,79 @@
         <v>2</v>
       </c>
       <c r="B7" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C7" s="0">
-        <v>0.00092386585576805468</v>
+        <v>0.0010278580951742877</v>
       </c>
       <c r="D7" s="0">
-        <v>0.0051046165257119733</v>
+        <v>0.0052504385227599443</v>
       </c>
       <c r="E7" s="0">
-        <v>0.0048220727102142565</v>
+        <v>0.0043701036758554352</v>
       </c>
       <c r="F7" s="0">
-        <v>0.80069108504127218</v>
+        <v>0.79854806110585019</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.012283411447464806</v>
+        <v>-0.01185021249090948</v>
       </c>
       <c r="H7" s="0">
-        <v>0.78797220646588495</v>
+        <v>0.78684574138143615</v>
       </c>
       <c r="I7" s="0">
-        <v>0.0038234430987622537</v>
+        <v>0.0038042399244939476</v>
       </c>
       <c r="J7" s="0">
-        <v>7.9858164417800808</v>
+        <v>4.9016429495829117</v>
       </c>
       <c r="K7" s="0">
-        <v>-0.0036883022907283078</v>
+        <v>-0.0035321872687454829</v>
       </c>
       <c r="L7" s="0">
-        <v>0.0039214030032957026</v>
+        <v>0.004075113079894453</v>
       </c>
       <c r="M7" s="0">
-        <v>0.00062982242928778798</v>
+        <v>0.00023324608656699174</v>
       </c>
       <c r="N7" s="0">
-        <v>0.70389404058719574</v>
+        <v>0.70279484075612408</v>
       </c>
       <c r="O7" s="0">
-        <v>-0.019466059688426247</v>
+        <v>-0.018963397284384918</v>
       </c>
       <c r="P7" s="0">
-        <v>0.78008203032057777</v>
+        <v>0.77899820646818863</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.0015025361071070915</v>
+        <v>0.0015054088419306391</v>
       </c>
       <c r="R7" s="0">
-        <v>6.5667345952727532</v>
+        <v>3.6690004109269374</v>
       </c>
       <c r="S7" s="0">
-        <v>0.0055360340022644174</v>
+        <v>0.0055879034590940579</v>
       </c>
       <c r="T7" s="0">
-        <v>0.0062878300481282439</v>
+        <v>0.0064257639656254357</v>
       </c>
       <c r="U7" s="0">
-        <v>0.009014322991140725</v>
+        <v>0.0085069612651438795</v>
       </c>
       <c r="V7" s="0">
-        <v>0.89748812949534862</v>
+        <v>0.8943012814555763</v>
       </c>
       <c r="W7" s="0">
-        <v>-0.005100763206503366</v>
+        <v>-0.0047370276974340441</v>
       </c>
       <c r="X7" s="0">
-        <v>0.79586238261119213</v>
+        <v>0.79469327629468367</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.0061443500904174164</v>
+        <v>0.0061030710070572557</v>
       </c>
       <c r="Z7" s="0">
-        <v>9.4048982882874075</v>
+        <v>6.134285488238886</v>
       </c>
       <c r="AA7" s="0"/>
       <c r="AB7" s="0"/>
@@ -858,79 +861,79 @@
         <v>2</v>
       </c>
       <c r="B8" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C8" s="0">
-        <v>0.010885850102746248</v>
+        <v>0.012288814410340307</v>
       </c>
       <c r="D8" s="0">
-        <v>0.0037926595520403647</v>
+        <v>0.0068184693343833706</v>
       </c>
       <c r="E8" s="0">
-        <v>0.0085475114728210608</v>
+        <v>0.013539390923256244</v>
       </c>
       <c r="F8" s="0">
-        <v>0.68300634352365131</v>
+        <v>0.70023205153129609</v>
       </c>
       <c r="G8" s="0">
-        <v>-0.01007860741944072</v>
+        <v>-0.0052795791675551256</v>
       </c>
       <c r="H8" s="0">
-        <v>0.78630232255653532</v>
+        <v>0.78888207455326687</v>
       </c>
       <c r="I8" s="0">
-        <v>0.011481102745694249</v>
+        <v>0.012731609799617018</v>
       </c>
       <c r="J8" s="0">
-        <v>2.6356551618877724</v>
+        <v>0.32476189072459311</v>
       </c>
       <c r="K8" s="0">
-        <v>0.0067423814184362982</v>
+        <v>0.0068653386234190173</v>
       </c>
       <c r="L8" s="0">
-        <v>0.0024362034208628503</v>
+        <v>0.0050697949972054752</v>
       </c>
       <c r="M8" s="0">
-        <v>0.0049184844056796677</v>
+        <v>0.0088597373184038323</v>
       </c>
       <c r="N8" s="0">
-        <v>0.60314907653626426</v>
+        <v>0.58947431960157681</v>
       </c>
       <c r="O8" s="0">
-        <v>-0.016211354299034978</v>
+        <v>-0.013672377264492046</v>
       </c>
       <c r="P8" s="0">
-        <v>0.77978262043677482</v>
+        <v>0.78032036836952024</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.0084959625748527289</v>
+        <v>0.0088250888824111598</v>
       </c>
       <c r="R8" s="0">
-        <v>1.885667288071228</v>
+        <v>-0.55099473692920853</v>
       </c>
       <c r="S8" s="0">
-        <v>0.015029318787056198</v>
+        <v>0.017712290197261598</v>
       </c>
       <c r="T8" s="0">
-        <v>0.0051491156832178791</v>
+        <v>0.008567143671561266</v>
       </c>
       <c r="U8" s="0">
-        <v>0.012176538539962454</v>
+        <v>0.018219044528108658</v>
       </c>
       <c r="V8" s="0">
-        <v>0.76286361051103835</v>
+        <v>0.81098978346101536</v>
       </c>
       <c r="W8" s="0">
-        <v>-0.0039458605398464608</v>
+        <v>0.0031132189293817947</v>
       </c>
       <c r="X8" s="0">
-        <v>0.79282202467629581</v>
+        <v>0.7974437807370135</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.01446624291653577</v>
+        <v>0.016638130716822876</v>
       </c>
       <c r="Z8" s="0">
-        <v>3.3856430357043168</v>
+        <v>1.2005185183783946</v>
       </c>
       <c r="AA8" s="0"/>
       <c r="AB8" s="0"/>
@@ -946,79 +949,79 @@
         <v>3</v>
       </c>
       <c r="B9" s="0">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C9" s="0">
-        <v>0.0041583967243602107</v>
+        <v>0.0049294823343776885</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.0038536124723047181</v>
+        <v>-0.0038546559738495026</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.00061082504668464601</v>
+        <v>-0.00057437811787119551</v>
       </c>
       <c r="F9" s="0">
-        <v>0.71437198331333263</v>
+        <v>0.72006212692952332</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.02396976280794343</v>
+        <v>-0.024522033012010145</v>
       </c>
       <c r="H9" s="0">
-        <v>0.77926312591219216</v>
+        <v>0.7792062865859154</v>
       </c>
       <c r="I9" s="0">
-        <v>0.007721571079848848</v>
+        <v>0.0077294229362769723</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.29717081819581048</v>
+        <v>-2.5460942727930274</v>
       </c>
       <c r="K9" s="0">
-        <v>0.0010272278156979015</v>
+        <v>0.0017956868871125886</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.0040295137568664968</v>
+        <v>-0.0040304021949728866</v>
       </c>
       <c r="M9" s="0">
-        <v>-0.00079111116013829926</v>
+        <v>-0.00075476793468289547</v>
       </c>
       <c r="N9" s="0">
-        <v>0.69231914045656351</v>
+        <v>0.69783996833225526</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.026218130294046151</v>
+        <v>-0.026786880994326755</v>
       </c>
       <c r="P9" s="0">
-        <v>0.77447741555454253</v>
+        <v>0.77442636750031169</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.0072495590400039264</v>
+        <v>0.007257888612882883</v>
       </c>
       <c r="R9" s="0">
-        <v>-0.31072595246624729</v>
+        <v>-2.5586444327153863</v>
       </c>
       <c r="S9" s="0">
-        <v>0.0072895656330225194</v>
+        <v>0.0080632777816427893</v>
       </c>
       <c r="T9" s="0">
-        <v>-0.0036777111877429394</v>
+        <v>-0.0036789097527261186</v>
       </c>
       <c r="U9" s="0">
-        <v>-0.00043053893323099276</v>
+        <v>-0.00039398830105949549</v>
       </c>
       <c r="V9" s="0">
-        <v>0.73642482617010174</v>
+        <v>0.74228428552679138</v>
       </c>
       <c r="W9" s="0">
-        <v>-0.021721395321840708</v>
+        <v>-0.022257185029693535</v>
       </c>
       <c r="X9" s="0">
-        <v>0.78404883626984179</v>
+        <v>0.78398620567151911</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.0081935831196937696</v>
+        <v>0.0082009572596710625</v>
       </c>
       <c r="Z9" s="0">
-        <v>-0.28361568392537367</v>
+        <v>-2.5335441128706684</v>
       </c>
       <c r="AA9" s="0"/>
       <c r="AB9" s="0"/>
@@ -1034,79 +1037,79 @@
         <v>3</v>
       </c>
       <c r="B10" s="0">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C10" s="0">
-        <v>0.01533660770618357</v>
+        <v>0.017453062827398311</v>
       </c>
       <c r="D10" s="0">
-        <v>0.00050946661500639128</v>
+        <v>0.00032534118956346767</v>
       </c>
       <c r="E10" s="0">
-        <v>0.00064017647079376184</v>
+        <v>0.0006609445701649412</v>
       </c>
       <c r="F10" s="0">
-        <v>0.74337825860198059</v>
+        <v>0.74527824047804259</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.017122200596019068</v>
+        <v>-0.017697053563691903</v>
       </c>
       <c r="H10" s="0">
-        <v>0.78226757012630011</v>
+        <v>0.81016317724094522</v>
       </c>
       <c r="I10" s="0">
-        <v>0.0066009561898845194</v>
+        <v>0.0068696040708020748</v>
       </c>
       <c r="J10" s="0">
-        <v>-0.03695832521044834</v>
+        <v>-2.254110139666027</v>
       </c>
       <c r="K10" s="0">
-        <v>0.013091287876697274</v>
+        <v>0.015062909154127181</v>
       </c>
       <c r="L10" s="0">
-        <v>0.00039605053593986546</v>
+        <v>0.00020579103130151223</v>
       </c>
       <c r="M10" s="0">
-        <v>0.00052831487452158828</v>
+        <v>0.00054269098538922342</v>
       </c>
       <c r="N10" s="0">
-        <v>0.7398213710030066</v>
+        <v>0.7415028553156181</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.017607494169486558</v>
+        <v>-0.018211058075908546</v>
       </c>
       <c r="P10" s="0">
-        <v>0.77620673278297625</v>
+        <v>0.8034834317666546</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.0061781320130268862</v>
+        <v>0.0064196590554763773</v>
       </c>
       <c r="R10" s="0">
-        <v>-0.042785915856796662</v>
+        <v>-2.259893730313737</v>
       </c>
       <c r="S10" s="0">
-        <v>0.017581927535669867</v>
+        <v>0.01984321650066944</v>
       </c>
       <c r="T10" s="0">
-        <v>0.00062288269407291715</v>
+        <v>0.00044489134782542308</v>
       </c>
       <c r="U10" s="0">
-        <v>0.00075203806706593539</v>
+        <v>0.00077919815494065898</v>
       </c>
       <c r="V10" s="0">
-        <v>0.74693514620095458</v>
+        <v>0.74905362564046707</v>
       </c>
       <c r="W10" s="0">
-        <v>-0.016636907022551578</v>
+        <v>-0.017183049051475261</v>
       </c>
       <c r="X10" s="0">
-        <v>0.78832840746962396</v>
+        <v>0.81684292271523584</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.0070237803667421526</v>
+        <v>0.0073195490861277723</v>
       </c>
       <c r="Z10" s="0">
-        <v>-0.03113073456410002</v>
+        <v>-2.2483265490183171</v>
       </c>
       <c r="AA10" s="0"/>
       <c r="AB10" s="0"/>
@@ -1122,79 +1125,79 @@
         <v>3</v>
       </c>
       <c r="B11" s="0">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C11" s="0">
-        <v>0.0043750838059252598</v>
+        <v>0.0083836924300078122</v>
       </c>
       <c r="D11" s="0">
-        <v>0.003855096591234597</v>
+        <v>0.002076286916131325</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.034906582811064374</v>
+        <v>-0.034906299629696269</v>
       </c>
       <c r="F11" s="0">
-        <v>0.70745813062978902</v>
+        <v>0.6492925557576833</v>
       </c>
       <c r="G11" s="0">
-        <v>-0.0058628365542440636</v>
+        <v>-0.0047402659366508424</v>
       </c>
       <c r="H11" s="0">
-        <v>0.77684449305774583</v>
+        <v>0.7867464484381691</v>
       </c>
       <c r="I11" s="0">
-        <v>0.00098673745819003985</v>
+        <v>0.011529530704221289</v>
       </c>
       <c r="J11" s="0">
-        <v>3.972782877571198</v>
+        <v>-4.1912194018938633</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.0010195216857747909</v>
+        <v>0.00033335756796099361</v>
       </c>
       <c r="L11" s="0">
-        <v>0.0013962174191912932</v>
+        <v>-0.0015424400421587621</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.04237299684731994</v>
+        <v>-0.04423885012740475</v>
       </c>
       <c r="N11" s="0">
-        <v>0.64137178270156281</v>
+        <v>0.55293928583622987</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.013193292182913485</v>
+        <v>-0.015488849814418818</v>
       </c>
       <c r="P11" s="0">
-        <v>0.76868720017837067</v>
+        <v>0.77440368676014082</v>
       </c>
       <c r="Q11" s="0">
-        <v>-0.0042874724337891735</v>
+        <v>0.0037917687324036829</v>
       </c>
       <c r="R11" s="0">
-        <v>2.5251110061638506</v>
+        <v>-5.6210264092675786</v>
       </c>
       <c r="S11" s="0">
-        <v>0.0097696892976253114</v>
+        <v>0.016434027292054631</v>
       </c>
       <c r="T11" s="0">
-        <v>0.0063139757632779004</v>
+        <v>0.0056950138744214125</v>
       </c>
       <c r="U11" s="0">
-        <v>-0.027440168774808808</v>
+        <v>-0.025573749131987792</v>
       </c>
       <c r="V11" s="0">
-        <v>0.77354447855801523</v>
+        <v>0.74564582567913673</v>
       </c>
       <c r="W11" s="0">
-        <v>0.0014676190744253581</v>
+        <v>0.006008317941117133</v>
       </c>
       <c r="X11" s="0">
-        <v>0.785001785937121</v>
+        <v>0.79908921011619738</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.0062609473501692541</v>
+        <v>0.019267292676038893</v>
       </c>
       <c r="Z11" s="0">
-        <v>5.4204547489785453</v>
+        <v>-2.7614123945201481</v>
       </c>
       <c r="AA11" s="0"/>
       <c r="AB11" s="0"/>
@@ -1210,79 +1213,79 @@
         <v>4</v>
       </c>
       <c r="B12" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C12" s="0">
-        <v>0.017453219229896177</v>
+        <v>0.01745305517339997</v>
       </c>
       <c r="D12" s="0">
-        <v>0.0046725439003982528</v>
+        <v>0.0046848932904817202</v>
       </c>
       <c r="E12" s="0">
-        <v>0.0016674587423236276</v>
+        <v>0.0015013170715910704</v>
       </c>
       <c r="F12" s="0">
-        <v>0.86002224227047186</v>
+        <v>0.86075898160345377</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.019661809766329672</v>
+        <v>-0.019600030481600025</v>
       </c>
       <c r="H12" s="0">
-        <v>0.76677801824794611</v>
+        <v>0.76685599261065984</v>
       </c>
       <c r="I12" s="0">
-        <v>0.0053655283253346555</v>
+        <v>0.0056681993134317299</v>
       </c>
       <c r="J12" s="0">
-        <v>-0.3398236245130154</v>
+        <v>-2.4532826486946644</v>
       </c>
       <c r="K12" s="0">
-        <v>0.013711400381021288</v>
+        <v>0.013727821934431275</v>
       </c>
       <c r="L12" s="0">
-        <v>0.0044336680251024288</v>
+        <v>0.0044467604739314827</v>
       </c>
       <c r="M12" s="0">
-        <v>0.0014254027485168666</v>
+        <v>0.0012603153338210697</v>
       </c>
       <c r="N12" s="0">
-        <v>0.84042749564163854</v>
+        <v>0.84120706472409279</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.021768978443207986</v>
+        <v>-0.021699622205759064</v>
       </c>
       <c r="P12" s="0">
-        <v>0.76078214752986406</v>
+        <v>0.76088123629476001</v>
       </c>
       <c r="Q12" s="0">
-        <v>0.0046146088440916595</v>
+        <v>0.0049188857410360958</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.35747011018888314</v>
+        <v>-2.4694321245863824</v>
       </c>
       <c r="S12" s="0">
-        <v>0.021195038078771066</v>
+        <v>0.021178288412368663</v>
       </c>
       <c r="T12" s="0">
-        <v>0.0049114197756940769</v>
+        <v>0.0049230261070319576</v>
       </c>
       <c r="U12" s="0">
-        <v>0.0019095147361303886</v>
+        <v>0.0017423188093610711</v>
       </c>
       <c r="V12" s="0">
-        <v>0.87961698889930518</v>
+        <v>0.88031089848281474</v>
       </c>
       <c r="W12" s="0">
-        <v>-0.017554641089451359</v>
+        <v>-0.017500438757440985</v>
       </c>
       <c r="X12" s="0">
-        <v>0.77277388896602817</v>
+        <v>0.77283074892655967</v>
       </c>
       <c r="Y12" s="0">
-        <v>0.0061164478065776516</v>
+        <v>0.0064175128858273639</v>
       </c>
       <c r="Z12" s="0">
-        <v>-0.32217713883714766</v>
+        <v>-2.4371331728029464</v>
       </c>
       <c r="AA12" s="0"/>
       <c r="AB12" s="0"/>
@@ -1298,79 +1301,79 @@
         <v>4</v>
       </c>
       <c r="B13" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C13" s="0">
-        <v>0.0059280148711249713</v>
+        <v>0.0059293932258079399</v>
       </c>
       <c r="D13" s="0">
-        <v>0.0020836308876135156</v>
+        <v>0.0021447171031506269</v>
       </c>
       <c r="E13" s="0">
-        <v>0.0013291485771579352</v>
+        <v>0.0013379236269897489</v>
       </c>
       <c r="F13" s="0">
-        <v>0.85615888642614568</v>
+        <v>0.85464513404652143</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.026355107390931654</v>
+        <v>-0.026059670277124018</v>
       </c>
       <c r="H13" s="0">
-        <v>0.7475882997265797</v>
+        <v>0.76347824522548735</v>
       </c>
       <c r="I13" s="0">
-        <v>0.0014755085276827408</v>
+        <v>0.0016029421132122575</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.12411931797857205</v>
+        <v>-2.2498716285888949</v>
       </c>
       <c r="K13" s="0">
-        <v>0.0010705153513174909</v>
+        <v>0.0012643181108731834</v>
       </c>
       <c r="L13" s="0">
-        <v>0.0018580401057492753</v>
+        <v>0.0019286537190288148</v>
       </c>
       <c r="M13" s="0">
-        <v>0.0011098943575592666</v>
+        <v>0.0011280175941366685</v>
       </c>
       <c r="N13" s="0">
-        <v>0.84877983526052825</v>
+        <v>0.84757101910743515</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.027387740724083218</v>
+        <v>-0.027049960345377308</v>
       </c>
       <c r="P13" s="0">
-        <v>0.73170173774468394</v>
+        <v>0.74801753424269957</v>
       </c>
       <c r="Q13" s="0">
-        <v>0.00051957359693336695</v>
+        <v>0.00068330924218769459</v>
       </c>
       <c r="R13" s="0">
-        <v>-0.13658723435922737</v>
+        <v>-2.2609872110124476</v>
       </c>
       <c r="S13" s="0">
-        <v>0.010785514390932453</v>
+        <v>0.010594468340742697</v>
       </c>
       <c r="T13" s="0">
-        <v>0.002309221669477756</v>
+        <v>0.0023607804872724392</v>
       </c>
       <c r="U13" s="0">
-        <v>0.0015484027967566038</v>
+        <v>0.0015478296598428294</v>
       </c>
       <c r="V13" s="0">
-        <v>0.86353793759176312</v>
+        <v>0.8617192489856077</v>
       </c>
       <c r="W13" s="0">
-        <v>-0.025322474057780091</v>
+        <v>-0.025069380208870729</v>
       </c>
       <c r="X13" s="0">
-        <v>0.76347486170847545</v>
+        <v>0.77893895620827514</v>
       </c>
       <c r="Y13" s="0">
-        <v>0.0024314434584321145</v>
+        <v>0.0025225749842368202</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0.11165140159791673</v>
+        <v>-2.2387560461653422</v>
       </c>
       <c r="AA13" s="0"/>
       <c r="AB13" s="0"/>
@@ -1386,79 +1389,79 @@
         <v>4</v>
       </c>
       <c r="B14" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C14" s="0">
-        <v>0.017453292511261598</v>
+        <v>0.017453292509990673</v>
       </c>
       <c r="D14" s="0">
-        <v>0.0092716172182242367</v>
+        <v>0.0086898908493166296</v>
       </c>
       <c r="E14" s="0">
-        <v>-0.00071929598988773093</v>
+        <v>0.00018636219735431293</v>
       </c>
       <c r="F14" s="0">
-        <v>0.73677601153753103</v>
+        <v>0.73780267991474735</v>
       </c>
       <c r="G14" s="0">
-        <v>0.0024434088381772843</v>
+        <v>0.0012129845636887214</v>
       </c>
       <c r="H14" s="0">
-        <v>0.97111492772343766</v>
+        <v>0.98375728122116524</v>
       </c>
       <c r="I14" s="0">
-        <v>0.011157280617098997</v>
+        <v>0.0093706965611656274</v>
       </c>
       <c r="J14" s="0">
-        <v>0.34457879128216779</v>
+        <v>-1.7015658840123766</v>
       </c>
       <c r="K14" s="0">
-        <v>0.0094037815957136763</v>
+        <v>0.0093802733883478814</v>
       </c>
       <c r="L14" s="0">
-        <v>0.0080454930148425446</v>
+        <v>0.0074675770129922301</v>
       </c>
       <c r="M14" s="0">
-        <v>-0.0019309891363610068</v>
+        <v>-0.0010279844675760296</v>
       </c>
       <c r="N14" s="0">
-        <v>0.72355645056385498</v>
+        <v>0.72454533824344802</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.00036911263280190029</v>
+        <v>-0.0015874699360873515</v>
       </c>
       <c r="P14" s="0">
-        <v>0.93706000171390469</v>
+        <v>0.94900848243319447</v>
       </c>
       <c r="Q14" s="0">
-        <v>0.0085620751209391187</v>
+        <v>0.0067677307131187858</v>
       </c>
       <c r="R14" s="0">
-        <v>0.30143529740722363</v>
+        <v>-1.7417428528460779</v>
       </c>
       <c r="S14" s="0">
-        <v>0.025502803426809519</v>
+        <v>0.025526311631633464</v>
       </c>
       <c r="T14" s="0">
-        <v>0.010497741421605929</v>
+        <v>0.0099122046856410292</v>
       </c>
       <c r="U14" s="0">
-        <v>0.00049239715658554487</v>
+        <v>0.0014007088622846552</v>
       </c>
       <c r="V14" s="0">
-        <v>0.74999557251120708</v>
+        <v>0.75106002158604668</v>
       </c>
       <c r="W14" s="0">
-        <v>0.0052559303091564685</v>
+        <v>0.0040134390634647948</v>
       </c>
       <c r="X14" s="0">
-        <v>1.0051698537329707</v>
+        <v>1.0185060800091359</v>
       </c>
       <c r="Y14" s="0">
-        <v>0.013752486113258876</v>
+        <v>0.011973662409212469</v>
       </c>
       <c r="Z14" s="0">
-        <v>0.38772228515711194</v>
+        <v>-1.6613889151786754</v>
       </c>
       <c r="AA14" s="0"/>
       <c r="AB14" s="0"/>
@@ -1474,79 +1477,79 @@
         <v>4</v>
       </c>
       <c r="B15" s="0">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C15" s="0">
-        <v>0.0061443380700334097</v>
+        <v>0.0066863609243270894</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.017453292519425949</v>
+        <v>-0.017453292519092802</v>
       </c>
       <c r="E15" s="0">
-        <v>-0.0057788673842583691</v>
+        <v>-0.0015212601146836085</v>
       </c>
       <c r="F15" s="0">
-        <v>0.72644656961671272</v>
+        <v>0.76145048996755227</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.048635072109916085</v>
+        <v>-0.051911128643372384</v>
       </c>
       <c r="H15" s="0">
-        <v>0.79456774951277209</v>
+        <v>0.79952225706923252</v>
       </c>
       <c r="I15" s="0">
-        <v>0.010664065481723634</v>
+        <v>0.011787548345596316</v>
       </c>
       <c r="J15" s="0">
-        <v>5.258020501155233</v>
+        <v>1.053016251307866</v>
       </c>
       <c r="K15" s="0">
-        <v>0.0019717609762513778</v>
+        <v>0.002478631636432329</v>
       </c>
       <c r="L15" s="0">
-        <v>-0.019926155224890791</v>
+        <v>-0.019954005140709535</v>
       </c>
       <c r="M15" s="0">
-        <v>-0.01260676452015469</v>
+        <v>-0.008353906791460473</v>
       </c>
       <c r="N15" s="0">
-        <v>0.66530948983677252</v>
+        <v>0.69733305263909873</v>
       </c>
       <c r="O15" s="0">
-        <v>-0.056143140072090758</v>
+        <v>-0.059662223148644528</v>
       </c>
       <c r="P15" s="0">
-        <v>0.78771096690985054</v>
+        <v>0.79254836178600507</v>
       </c>
       <c r="Q15" s="0">
-        <v>0.0057149965748189467</v>
+        <v>0.0067783718009484959</v>
       </c>
       <c r="R15" s="0">
-        <v>4.0930209428220437</v>
+        <v>0.020983323021948053</v>
       </c>
       <c r="S15" s="0">
-        <v>0.010316915163815442</v>
+        <v>0.01089409021222185</v>
       </c>
       <c r="T15" s="0">
-        <v>-0.014980429813961107</v>
+        <v>-0.01495257989747607</v>
       </c>
       <c r="U15" s="0">
-        <v>0.0010490297516379515</v>
+        <v>0.0053113865620932552</v>
       </c>
       <c r="V15" s="0">
-        <v>0.78758364939665293</v>
+        <v>0.82556792729600581</v>
       </c>
       <c r="W15" s="0">
-        <v>-0.041127004147741411</v>
+        <v>-0.04416003413810024</v>
       </c>
       <c r="X15" s="0">
-        <v>0.80142453211569365</v>
+        <v>0.80649615235245997</v>
       </c>
       <c r="Y15" s="0">
-        <v>0.015613134388628321</v>
+        <v>0.016796724890244134</v>
       </c>
       <c r="Z15" s="0">
-        <v>6.4230200594884224</v>
+        <v>2.085049179593784</v>
       </c>
       <c r="AA15" s="0"/>
       <c r="AB15" s="0"/>
@@ -1558,32 +1561,84 @@
       <c r="AH15" s="0"/>
     </row>
     <row r="16">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0"/>
-      <c r="K16" s="0"/>
-      <c r="L16" s="0"/>
-      <c r="M16" s="0"/>
-      <c r="N16" s="0"/>
-      <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
-      <c r="S16" s="0"/>
-      <c r="T16" s="0"/>
-      <c r="U16" s="0"/>
-      <c r="V16" s="0"/>
-      <c r="W16" s="0"/>
-      <c r="X16" s="0"/>
-      <c r="Y16" s="0"/>
-      <c r="Z16" s="0"/>
+      <c r="A16" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="0">
+        <v>462</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0.013590960572112423</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0.00031133038832832503</v>
+      </c>
+      <c r="E16" s="0">
+        <v>-5.6037777119985108e-05</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0.69966281258064744</v>
+      </c>
+      <c r="G16" s="0">
+        <v>-0.010931965346342014</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0.78742864407039836</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0.011555462483675132</v>
+      </c>
+      <c r="J16" s="0">
+        <v>-2.6264725803804212</v>
+      </c>
+      <c r="K16" s="0">
+        <v>0.0097394101854487679</v>
+      </c>
+      <c r="L16" s="0">
+        <v>1.52784539276951e-05</v>
+      </c>
+      <c r="M16" s="0">
+        <v>-0.00035463691869899977</v>
+      </c>
+      <c r="N16" s="0">
+        <v>0.66495016517453309</v>
+      </c>
+      <c r="O16" s="0">
+        <v>-0.014112204966983604</v>
+      </c>
+      <c r="P16" s="0">
+        <v>0.781270791718506</v>
+      </c>
+      <c r="Q16" s="0">
+        <v>0.010811712084108756</v>
+      </c>
+      <c r="R16" s="0">
+        <v>-2.6494769232063709</v>
+      </c>
+      <c r="S16" s="0">
+        <v>0.017442510958776077</v>
+      </c>
+      <c r="T16" s="0">
+        <v>0.00060738232272895495</v>
+      </c>
+      <c r="U16" s="0">
+        <v>0.00024256136445902955</v>
+      </c>
+      <c r="V16" s="0">
+        <v>0.73437545998676179</v>
+      </c>
+      <c r="W16" s="0">
+        <v>-0.0077517257257004244</v>
+      </c>
+      <c r="X16" s="0">
+        <v>0.79358649642229073</v>
+      </c>
+      <c r="Y16" s="0">
+        <v>0.012299212883241508</v>
+      </c>
+      <c r="Z16" s="0">
+        <v>-2.6034682375544716</v>
+      </c>
       <c r="AA16" s="0"/>
       <c r="AB16" s="0"/>
       <c r="AC16" s="0"/>
@@ -1597,78 +1652,80 @@
       <c r="A17" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="0"/>
+      <c r="B17" s="0">
+        <v>462</v>
+      </c>
       <c r="C17" s="0">
-        <v>0.010397692775527207</v>
+        <v>0.017453289943470052</v>
       </c>
       <c r="D17" s="0">
-        <v>0.0027609987260931571</v>
+        <v>-0.0043211321753232864</v>
       </c>
       <c r="E17" s="0">
-        <v>-0.0011378340706119268</v>
+        <v>0.0026765517776769772</v>
       </c>
       <c r="F17" s="0">
-        <v>0.74760238700613557</v>
+        <v>0.75007396344564792</v>
       </c>
       <c r="G17" s="0">
-        <v>-0.012942012746269115</v>
+        <v>-0.025739888383358448</v>
       </c>
       <c r="H17" s="0">
-        <v>0.77503611960066598</v>
+        <v>0.60931946813829863</v>
       </c>
       <c r="I17" s="0">
-        <v>0.0054267117321361857</v>
+        <v>0.0026516976666205458</v>
       </c>
       <c r="J17" s="0">
-        <v>0.091482455797930226</v>
+        <v>-2.5293731459450539</v>
       </c>
       <c r="K17" s="0">
-        <v>0.0055373343970319859</v>
+        <v>0.013866169687344002</v>
       </c>
       <c r="L17" s="0">
-        <v>0.0017169799533122943</v>
+        <v>-0.0045100438999039674</v>
       </c>
       <c r="M17" s="0">
-        <v>-0.0040551419603008379</v>
+        <v>0.0024917171311663634</v>
       </c>
       <c r="N17" s="0">
-        <v>0.69832728629568164</v>
+        <v>0.74480845760674985</v>
       </c>
       <c r="O17" s="0">
-        <v>-0.017526215161147812</v>
+        <v>-0.026371166934604468</v>
       </c>
       <c r="P17" s="0">
-        <v>0.76385003921020111</v>
+        <v>0.59525912295097905</v>
       </c>
       <c r="Q17" s="0">
-        <v>0.0031235551837530307</v>
+        <v>0.0021002945315948423</v>
       </c>
       <c r="R17" s="0">
-        <v>-0.5294552099418296</v>
+        <v>-2.5402420411811022</v>
       </c>
       <c r="S17" s="0">
-        <v>0.015258051154022427</v>
+        <v>0.021040410199596103</v>
       </c>
       <c r="T17" s="0">
-        <v>0.0038050174988740202</v>
+        <v>-0.0041322204507426054</v>
       </c>
       <c r="U17" s="0">
-        <v>0.0017794738190769824</v>
+        <v>0.0028613864241875909</v>
       </c>
       <c r="V17" s="0">
-        <v>0.79687748771658984</v>
+        <v>0.75533946928454598</v>
       </c>
       <c r="W17" s="0">
-        <v>-0.0083578103313904206</v>
+        <v>-0.025108609832112428</v>
       </c>
       <c r="X17" s="0">
-        <v>0.78622219999113086</v>
+        <v>0.6233798133256182</v>
       </c>
       <c r="Y17" s="0">
-        <v>0.007729868280519343</v>
+        <v>0.0032031008016462493</v>
       </c>
       <c r="Z17" s="0">
-        <v>0.71242012153768974</v>
+        <v>-2.5185042507090056</v>
       </c>
       <c r="AA17" s="0"/>
       <c r="AB17" s="0"/>
@@ -1681,80 +1738,82 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="0"/>
+        <v>5</v>
+      </c>
+      <c r="B18" s="0">
+        <v>462</v>
+      </c>
       <c r="C18" s="0">
-        <v>0.0065015674177380826</v>
+        <v>0.0020057457879243054</v>
       </c>
       <c r="D18" s="0">
-        <v>0.0087830728879895927</v>
+        <v>-0.0066963541575014683</v>
       </c>
       <c r="E18" s="0">
-        <v>0.012276795588028256</v>
+        <v>-0.0014733219768185222</v>
       </c>
       <c r="F18" s="0">
-        <v>0.081186884086595579</v>
+        <v>0.83148290890679788</v>
       </c>
       <c r="G18" s="0">
-        <v>0.020489494147016615</v>
+        <v>-0.036473168711246791</v>
       </c>
       <c r="H18" s="0">
-        <v>0.069006229397747781</v>
+        <v>0.7074047538114272</v>
       </c>
       <c r="I18" s="0">
-        <v>0.0035907861796131112</v>
+        <v>0.0083012122996640164</v>
       </c>
       <c r="J18" s="0">
-        <v>4.4351757374015817</v>
+        <v>-2.4203872565552938</v>
       </c>
       <c r="K18" s="0">
-        <v>0.0079768484677627885</v>
+        <v>-0.0024935787026979699</v>
       </c>
       <c r="L18" s="0">
-        <v>0.0086030940313560952</v>
+        <v>-0.0068936968957802793</v>
       </c>
       <c r="M18" s="0">
-        <v>0.013944191670417588</v>
+        <v>-0.0016621132184515704</v>
       </c>
       <c r="N18" s="0">
-        <v>0.11855344276150329</v>
+        <v>0.82604760442376068</v>
       </c>
       <c r="O18" s="0">
-        <v>0.018258947869323514</v>
+        <v>-0.037127189849049072</v>
       </c>
       <c r="P18" s="0">
-        <v>0.065870059695426128</v>
+        <v>0.68614255192991891</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.0042937489597340457</v>
+        <v>0.0076307644919752964</v>
       </c>
       <c r="R18" s="0">
-        <v>4.5747043602061517</v>
+        <v>-2.4333545216182553</v>
       </c>
       <c r="S18" s="0">
-        <v>0.0060179921608553809</v>
+        <v>0.0065050702785465807</v>
       </c>
       <c r="T18" s="0">
-        <v>0.0090793521345831942</v>
+        <v>-0.0064990114192226573</v>
       </c>
       <c r="U18" s="0">
-        <v>0.011491074165993053</v>
+        <v>-0.001284530735185474</v>
       </c>
       <c r="V18" s="0">
-        <v>0.078168323331155753</v>
+        <v>0.83691821338983508</v>
       </c>
       <c r="W18" s="0">
-        <v>0.02347924220381074</v>
+        <v>-0.03581914757344451</v>
       </c>
       <c r="X18" s="0">
-        <v>0.072866323296130436</v>
+        <v>0.72866695569293549</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.0041295299334551559</v>
+        <v>0.0089716601073527372</v>
       </c>
       <c r="Z18" s="0">
-        <v>4.4387303276849011</v>
+        <v>-2.4074199914923322</v>
       </c>
       <c r="AA18" s="0"/>
       <c r="AB18" s="0"/>
@@ -1803,88 +1862,296 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="0"/>
       <c r="C20" s="0">
-        <v>0.017453292513164097</v>
+        <v>0.010603987995925398</v>
       </c>
       <c r="D20" s="0">
-        <v>-0.00057089804056733912</v>
+        <v>0.0018371605840431921</v>
       </c>
       <c r="E20" s="0">
-        <v>-0.000568744645598793</v>
+        <v>0.001060999041204151</v>
       </c>
       <c r="F20" s="0">
-        <v>0.7710967609274898</v>
+        <v>0.71816980169330757</v>
       </c>
       <c r="G20" s="0">
-        <v>-0.020828066719061161</v>
+        <v>-0.013378863011054828</v>
       </c>
       <c r="H20" s="0">
-        <v>0.76781532726080359</v>
+        <v>0.73668906581123284</v>
       </c>
       <c r="I20" s="0">
-        <v>0.0048761525870936505</v>
+        <v>0.0060269843665620168</v>
       </c>
       <c r="J20" s="0">
-        <v>-0.4746453244966028</v>
-      </c>
-      <c r="K20" s="0"/>
-      <c r="L20" s="0"/>
-      <c r="M20" s="0"/>
-      <c r="N20" s="0"/>
-      <c r="O20" s="0"/>
-      <c r="P20" s="0"/>
-      <c r="Q20" s="0"/>
-      <c r="R20" s="0"/>
+        <v>-2.348994905526661</v>
+      </c>
+      <c r="K20" s="0">
+        <v>0.0055486957614623829</v>
+      </c>
+      <c r="L20" s="0">
+        <v>0.0010248841284185752</v>
+      </c>
+      <c r="M20" s="0">
+        <v>-0.0013133611067037622</v>
+      </c>
+      <c r="N20" s="0">
+        <v>0.67169181601507211</v>
+      </c>
+      <c r="O20" s="0">
+        <v>-0.017207353687568382</v>
+      </c>
+      <c r="P20" s="0">
+        <v>0.72270560131880624</v>
+      </c>
+      <c r="Q20" s="0">
+        <v>0.0039324022588973538</v>
+      </c>
+      <c r="R20" s="0">
+        <v>-2.7860680104170941</v>
+      </c>
       <c r="S20" s="0">
-        <v>0.018673228145556019</v>
+        <v>0.015141116557368186</v>
       </c>
       <c r="T20" s="0">
-        <v>-0.00048290366678096098</v>
+        <v>0.0027732089591284868</v>
       </c>
       <c r="U20" s="0">
-        <v>-0.00048060412778311887</v>
+        <v>0.003464945204404732</v>
       </c>
       <c r="V20" s="0">
-        <v>0.77337183458901759</v>
+        <v>0.76059815312514167</v>
       </c>
       <c r="W20" s="0">
-        <v>-0.020544972825856166</v>
+        <v>-0.0092662969026032233</v>
       </c>
       <c r="X20" s="0">
-        <v>0.77073532993273475</v>
+        <v>0.74796150851116328</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.0051028436270321165</v>
+        <v>0.0081317120897631858</v>
       </c>
       <c r="Z20" s="0">
-        <v>-0.46892554964112815</v>
-      </c>
-      <c r="AA20" s="0">
-        <v>0.016233356880772175</v>
-      </c>
-      <c r="AB20" s="0">
-        <v>-0.00065889241435371725</v>
-      </c>
-      <c r="AC20" s="0">
-        <v>-0.00065688516341446714</v>
-      </c>
-      <c r="AD20" s="0">
-        <v>0.76882168726596201</v>
-      </c>
-      <c r="AE20" s="0">
-        <v>-0.021111160612266155</v>
-      </c>
-      <c r="AF20" s="0">
-        <v>0.76489532458887244</v>
-      </c>
-      <c r="AG20" s="0">
-        <v>0.0046494615471551846</v>
-      </c>
-      <c r="AH20" s="0">
-        <v>-0.48036509935207744</v>
+        <v>-1.9129649308124648</v>
+      </c>
+      <c r="AA20" s="0"/>
+      <c r="AB20" s="0"/>
+      <c r="AC20" s="0"/>
+      <c r="AD20" s="0"/>
+      <c r="AE20" s="0"/>
+      <c r="AF20" s="0"/>
+      <c r="AG20" s="0"/>
+      <c r="AH20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="0"/>
+      <c r="C21" s="0">
+        <v>0.0069042906183865585</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0.0078238639865113608</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0.010008767751482562</v>
+      </c>
+      <c r="F21" s="0">
+        <v>0.15125938223127516</v>
+      </c>
+      <c r="G21" s="0">
+        <v>0.019978406513714048</v>
+      </c>
+      <c r="H21" s="0">
+        <v>0.15415578018631629</v>
+      </c>
+      <c r="I21" s="0">
+        <v>0.003897091013358645</v>
+      </c>
+      <c r="J21" s="0">
+        <v>3.8394392126834496</v>
+      </c>
+      <c r="K21" s="0">
+        <v>0.0087165576294649747</v>
+      </c>
+      <c r="L21" s="0">
+        <v>0.0078040002901861296</v>
+      </c>
+      <c r="M21" s="0">
+        <v>0.011335733049739113</v>
+      </c>
+      <c r="N21" s="0">
+        <v>0.16701524976711071</v>
+      </c>
+      <c r="O21" s="0">
+        <v>0.018580289023290963</v>
+      </c>
+      <c r="P21" s="0">
+        <v>0.15471977367704787</v>
+      </c>
+      <c r="Q21" s="0">
+        <v>0.0043651077542241528</v>
+      </c>
+      <c r="R21" s="0">
+        <v>4.2455931965382048</v>
+      </c>
+      <c r="S21" s="0">
+        <v>0.0060816021552828571</v>
+      </c>
+      <c r="T21" s="0">
+        <v>0.0082032275505418278</v>
+      </c>
+      <c r="U21" s="0">
+        <v>0.010223357225296843</v>
+      </c>
+      <c r="V21" s="0">
+        <v>0.15412498333677482</v>
+      </c>
+      <c r="W21" s="0">
+        <v>0.022717670174944589</v>
+      </c>
+      <c r="X21" s="0">
+        <v>0.15689050161869639</v>
+      </c>
+      <c r="Y21" s="0">
+        <v>0.0048679923473693388</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>3.6799753705253551</v>
+      </c>
+      <c r="AA21" s="0"/>
+      <c r="AB21" s="0"/>
+      <c r="AC21" s="0"/>
+      <c r="AD21" s="0"/>
+      <c r="AE21" s="0"/>
+      <c r="AF21" s="0"/>
+      <c r="AG21" s="0"/>
+      <c r="AH21" s="0"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0"/>
+      <c r="B22" s="0"/>
+      <c r="C22" s="0"/>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+      <c r="I22" s="0"/>
+      <c r="J22" s="0"/>
+      <c r="K22" s="0"/>
+      <c r="L22" s="0"/>
+      <c r="M22" s="0"/>
+      <c r="N22" s="0"/>
+      <c r="O22" s="0"/>
+      <c r="P22" s="0"/>
+      <c r="Q22" s="0"/>
+      <c r="R22" s="0"/>
+      <c r="S22" s="0"/>
+      <c r="T22" s="0"/>
+      <c r="U22" s="0"/>
+      <c r="V22" s="0"/>
+      <c r="W22" s="0"/>
+      <c r="X22" s="0"/>
+      <c r="Y22" s="0"/>
+      <c r="Z22" s="0"/>
+      <c r="AA22" s="0"/>
+      <c r="AB22" s="0"/>
+      <c r="AC22" s="0"/>
+      <c r="AD22" s="0"/>
+      <c r="AE22" s="0"/>
+      <c r="AF22" s="0"/>
+      <c r="AG22" s="0"/>
+      <c r="AH22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="0"/>
+      <c r="C23" s="0">
+        <v>0.017453292341473949</v>
+      </c>
+      <c r="D23" s="0">
+        <v>-0.00089248622465755401</v>
+      </c>
+      <c r="E23" s="0">
+        <v>-0.00025983456417563104</v>
+      </c>
+      <c r="F23" s="0">
+        <v>0.76921703161563626</v>
+      </c>
+      <c r="G23" s="0">
+        <v>-0.021018368309738019</v>
+      </c>
+      <c r="H23" s="0">
+        <v>0.78010356277878756</v>
+      </c>
+      <c r="I23" s="0">
+        <v>0.0053699786836855726</v>
+      </c>
+      <c r="J23" s="0">
+        <v>-2.5273953112572456</v>
+      </c>
+      <c r="K23" s="0"/>
+      <c r="L23" s="0"/>
+      <c r="M23" s="0"/>
+      <c r="N23" s="0"/>
+      <c r="O23" s="0"/>
+      <c r="P23" s="0"/>
+      <c r="Q23" s="0"/>
+      <c r="R23" s="0"/>
+      <c r="S23" s="0">
+        <v>0.018523315720472333</v>
+      </c>
+      <c r="T23" s="0">
+        <v>-0.00081757205272535471</v>
+      </c>
+      <c r="U23" s="0">
+        <v>-0.00018486191702488119</v>
+      </c>
+      <c r="V23" s="0">
+        <v>0.77126807312634249</v>
+      </c>
+      <c r="W23" s="0">
+        <v>-0.020770226037740064</v>
+      </c>
+      <c r="X23" s="0">
+        <v>0.78263874344898454</v>
+      </c>
+      <c r="Y23" s="0">
+        <v>0.0055625035863827547</v>
+      </c>
+      <c r="Z23" s="0">
+        <v>-2.5227183479310398</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>0.016383268962475564</v>
+      </c>
+      <c r="AB23" s="0">
+        <v>-0.00096740039658975332</v>
+      </c>
+      <c r="AC23" s="0">
+        <v>-0.00033480721132638088</v>
+      </c>
+      <c r="AD23" s="0">
+        <v>0.76716599010493003</v>
+      </c>
+      <c r="AE23" s="0">
+        <v>-0.021266510581735974</v>
+      </c>
+      <c r="AF23" s="0">
+        <v>0.77756838210859058</v>
+      </c>
+      <c r="AG23" s="0">
+        <v>0.0051774537809883905</v>
+      </c>
+      <c r="AH23" s="0">
+        <v>-2.5320722745834514</v>
       </c>
     </row>
   </sheetData>

--- a/processing26/results_all_SHIP.xlsx
+++ b/processing26/results_all_SHIP.xlsx
@@ -190,14 +190,14 @@
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="true"/>
     <col min="2" max="2" width="8.85546875" customWidth="true"/>
-    <col min="3" max="3" width="15.42578125" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
     <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="16.42578125" customWidth="true"/>
     <col min="6" max="6" width="12.7109375" customWidth="true"/>
     <col min="7" max="7" width="15.42578125" customWidth="true"/>
     <col min="8" max="8" width="12.7109375" customWidth="true"/>
-    <col min="9" max="9" width="16.42578125" customWidth="true"/>
-    <col min="10" max="10" width="12.7109375" customWidth="true"/>
+    <col min="9" max="9" width="15.7109375" customWidth="true"/>
+    <col min="10" max="10" width="13.42578125" customWidth="true"/>
     <col min="11" max="11" width="15.42578125" customWidth="true"/>
     <col min="12" max="12" width="15.7109375" customWidth="true"/>
     <col min="13" max="13" width="16.42578125" customWidth="true"/>
@@ -205,15 +205,15 @@
     <col min="15" max="15" width="15.42578125" customWidth="true"/>
     <col min="16" max="16" width="12.7109375" customWidth="true"/>
     <col min="17" max="17" width="15.7109375" customWidth="true"/>
-    <col min="18" max="18" width="13.7109375" customWidth="true"/>
+    <col min="18" max="18" width="13.42578125" customWidth="true"/>
     <col min="19" max="19" width="14.7109375" customWidth="true"/>
     <col min="20" max="20" width="16.42578125" customWidth="true"/>
     <col min="21" max="21" width="16.42578125" customWidth="true"/>
     <col min="22" max="22" width="12.7109375" customWidth="true"/>
-    <col min="23" max="23" width="15.42578125" customWidth="true"/>
+    <col min="23" max="23" width="15.7109375" customWidth="true"/>
     <col min="24" max="24" width="12.7109375" customWidth="true"/>
     <col min="25" max="25" width="14.7109375" customWidth="true"/>
-    <col min="26" max="26" width="12.42578125" customWidth="true"/>
+    <col min="26" max="26" width="12.7109375" customWidth="true"/>
     <col min="27" max="27" width="7.5703125" customWidth="true"/>
     <col min="28" max="28" width="7.5703125" customWidth="true"/>
     <col min="29" max="29" width="7.5703125" customWidth="true"/>
@@ -336,76 +336,76 @@
         <v>462</v>
       </c>
       <c r="C2" s="0">
-        <v>0.017453292503118167</v>
+        <v>0.017453292503010812</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.0035045775175928311</v>
+        <v>-0.0035155912999763838</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.0019269065282780632</v>
+        <v>-0.0019906604996778733</v>
       </c>
       <c r="F2" s="0">
-        <v>0.77182667038953667</v>
+        <v>0.77190001476163761</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.027662504189099553</v>
+        <v>-0.027687189544290652</v>
       </c>
       <c r="H2" s="0">
-        <v>0.79930779127102247</v>
+        <v>0.79741893037923417</v>
       </c>
       <c r="I2" s="0">
-        <v>0.0033760939254961994</v>
+        <v>0.003300132530899026</v>
       </c>
       <c r="J2" s="0">
-        <v>-2.6897576254184825</v>
+        <v>-3.0778043514926559</v>
       </c>
       <c r="K2" s="0">
-        <v>0.013959783163348203</v>
+        <v>0.013784506173630334</v>
       </c>
       <c r="L2" s="0">
-        <v>-0.0037429086687214893</v>
+        <v>-0.0037650514623637802</v>
       </c>
       <c r="M2" s="0">
-        <v>-0.0021627230217184327</v>
+        <v>-0.0022375009305003698</v>
       </c>
       <c r="N2" s="0">
-        <v>0.76612735532181941</v>
+        <v>0.76591194510561245</v>
       </c>
       <c r="O2" s="0">
-        <v>-0.028378446426564837</v>
+        <v>-0.028437707331846956</v>
       </c>
       <c r="P2" s="0">
-        <v>0.78596759786529713</v>
+        <v>0.78345943078631764</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.0028050973743456564</v>
+        <v>0.0027022156396513089</v>
       </c>
       <c r="R2" s="0">
-        <v>-2.7034892308390353</v>
+        <v>-3.0921766951271601</v>
       </c>
       <c r="S2" s="0">
-        <v>0.020946801842888132</v>
+        <v>0.02112207883239129</v>
       </c>
       <c r="T2" s="0">
-        <v>-0.0032662463664641728</v>
+        <v>-0.0032661311375889873</v>
       </c>
       <c r="U2" s="0">
-        <v>-0.0016910900348376934</v>
+        <v>-0.001743820068855377</v>
       </c>
       <c r="V2" s="0">
-        <v>0.77752598545725393</v>
+        <v>0.77788808441766277</v>
       </c>
       <c r="W2" s="0">
-        <v>-0.026946561951634269</v>
+        <v>-0.026936671756734348</v>
       </c>
       <c r="X2" s="0">
-        <v>0.81264798467674781</v>
+        <v>0.81137842997215071</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.0039470904766467424</v>
+        <v>0.0038980494221467431</v>
       </c>
       <c r="Z2" s="0">
-        <v>-2.6760260199979298</v>
+        <v>-3.0634320078581516</v>
       </c>
       <c r="AA2" s="0"/>
       <c r="AB2" s="0"/>
@@ -421,79 +421,79 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C3" s="0">
-        <v>0.017453292508419281</v>
+        <v>0.017453292508389104</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.0010649163750569277</v>
+        <v>-0.00107252867839738</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.00030878435440587535</v>
+        <v>-0.00034983993142522119</v>
       </c>
       <c r="F3" s="0">
-        <v>0.76827796976989438</v>
+        <v>0.76904685327509481</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.023652277855416216</v>
+        <v>-0.023734058792067119</v>
       </c>
       <c r="H3" s="0">
-        <v>0.7121597989929277</v>
+        <v>0.70961312089474316</v>
       </c>
       <c r="I3" s="0">
-        <v>0.0033596722537983952</v>
+        <v>0.0033427956713901735</v>
       </c>
       <c r="J3" s="0">
-        <v>-2.6057610040633295</v>
+        <v>-2.9391939948148713</v>
       </c>
       <c r="K3" s="0">
-        <v>0.013406404211997286</v>
+        <v>0.013269761117796352</v>
       </c>
       <c r="L3" s="0">
-        <v>-0.0013287877264740199</v>
+        <v>-0.0013448367954260953</v>
       </c>
       <c r="M3" s="0">
-        <v>-0.00056755322465398513</v>
+        <v>-0.000616892863005725</v>
       </c>
       <c r="N3" s="0">
-        <v>0.76177732432757927</v>
+        <v>0.7623210314091351</v>
       </c>
       <c r="O3" s="0">
-        <v>-0.024442642799519524</v>
+        <v>-0.024550513524443939</v>
       </c>
       <c r="P3" s="0">
-        <v>0.69802569549557458</v>
+        <v>0.69502885596320552</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.0027166878714351803</v>
+        <v>0.0026790832690112365</v>
       </c>
       <c r="R3" s="0">
-        <v>-2.6213264394403773</v>
+        <v>-2.9552569470540724</v>
       </c>
       <c r="S3" s="0">
-        <v>0.021500180804841278</v>
+        <v>0.021636823898981854</v>
       </c>
       <c r="T3" s="0">
-        <v>-0.00080104502363983554</v>
+        <v>-0.0008002205613686648</v>
       </c>
       <c r="U3" s="0">
-        <v>-5.001548415776557e-05</v>
+        <v>-8.2786999844717386e-05</v>
       </c>
       <c r="V3" s="0">
-        <v>0.77477861521220948</v>
+        <v>0.77577267514105452</v>
       </c>
       <c r="W3" s="0">
-        <v>-0.022861912911312909</v>
+        <v>-0.022917604059690299</v>
       </c>
       <c r="X3" s="0">
-        <v>0.72629390249028081</v>
+        <v>0.72419738582628079</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.0040026566361616106</v>
+        <v>0.0040065080737691104</v>
       </c>
       <c r="Z3" s="0">
-        <v>-2.5901955686862816</v>
+        <v>-2.9231310425756703</v>
       </c>
       <c r="AA3" s="0"/>
       <c r="AB3" s="0"/>
@@ -512,76 +512,76 @@
         <v>462</v>
       </c>
       <c r="C4" s="0">
-        <v>0.0046501606303478551</v>
+        <v>0.0043569542198648604</v>
       </c>
       <c r="D4" s="0">
-        <v>0.017453292481448529</v>
+        <v>0.017453292482396129</v>
       </c>
       <c r="E4" s="0">
-        <v>0.015199268627525471</v>
+        <v>0.010689768406852058</v>
       </c>
       <c r="F4" s="0">
-        <v>0.57059750408759324</v>
+        <v>0.57053090090347292</v>
       </c>
       <c r="G4" s="0">
-        <v>0.030017960252805207</v>
+        <v>0.03002891503195956</v>
       </c>
       <c r="H4" s="0">
-        <v>0.72796398033415599</v>
+        <v>0.72462170934379588</v>
       </c>
       <c r="I4" s="0">
-        <v>0.00044490183158667424</v>
+        <v>0.00010866340084473322</v>
       </c>
       <c r="J4" s="0">
-        <v>-14.404841049381711</v>
+        <v>-15.233422029930441</v>
       </c>
       <c r="K4" s="0">
-        <v>-0.0013490783997223404</v>
+        <v>-0.0015031601449942136</v>
       </c>
       <c r="L4" s="0">
-        <v>0.015962699974907096</v>
+        <v>0.016006660173749073</v>
       </c>
       <c r="M4" s="0">
-        <v>0.0094766742049893771</v>
+        <v>0.0051864988627910837</v>
       </c>
       <c r="N4" s="0">
-        <v>0.47106044093720434</v>
+        <v>0.47377068393970073</v>
       </c>
       <c r="O4" s="0">
-        <v>0.021028655682119722</v>
+        <v>0.021289673565823137</v>
       </c>
       <c r="P4" s="0">
-        <v>0.71658839807310748</v>
+        <v>0.71356689276337082</v>
       </c>
       <c r="Q4" s="0">
-        <v>-0.0025293531543174835</v>
+        <v>-0.0027839009740326043</v>
       </c>
       <c r="R4" s="0">
-        <v>-15.771476521935762</v>
+        <v>-16.531622260006032</v>
       </c>
       <c r="S4" s="0">
-        <v>0.01064939966041805</v>
+        <v>0.010217068584723935</v>
       </c>
       <c r="T4" s="0">
-        <v>0.018943884987989962</v>
+        <v>0.018899924791043184</v>
       </c>
       <c r="U4" s="0">
-        <v>0.020921863050061565</v>
+        <v>0.016193037950913033</v>
       </c>
       <c r="V4" s="0">
-        <v>0.67013456723798215</v>
+        <v>0.66729111786724515</v>
       </c>
       <c r="W4" s="0">
-        <v>0.039007264823490692</v>
+        <v>0.038768156498095979</v>
       </c>
       <c r="X4" s="0">
-        <v>0.7393395625952045</v>
+        <v>0.73567652592422095</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.003419156817490832</v>
+        <v>0.0030012277757220712</v>
       </c>
       <c r="Z4" s="0">
-        <v>-13.038205576827659</v>
+        <v>-13.935221799854851</v>
       </c>
       <c r="AA4" s="0"/>
       <c r="AB4" s="0"/>
@@ -597,79 +597,79 @@
         <v>1</v>
       </c>
       <c r="B5" s="0">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.004546906373325668</v>
+        <v>-0.0059250892074193739</v>
       </c>
       <c r="D5" s="0">
-        <v>0.016834725438301036</v>
+        <v>0.017453286265892824</v>
       </c>
       <c r="E5" s="0">
-        <v>0.01231799263419214</v>
+        <v>-0.0038963222654463774</v>
       </c>
       <c r="F5" s="0">
-        <v>0.66746577207515323</v>
+        <v>0.60987531831740749</v>
       </c>
       <c r="G5" s="0">
-        <v>0.022533561390315034</v>
+        <v>0.02796630474976897</v>
       </c>
       <c r="H5" s="0">
-        <v>0.67605420711769793</v>
+        <v>0.66137314363796584</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.00046149822129755419</v>
+        <v>-0.0028513059255658511</v>
       </c>
       <c r="J5" s="0">
-        <v>-6.9143631350981973</v>
+        <v>-13.20386851948702</v>
       </c>
       <c r="K5" s="0">
-        <v>-0.018942765836634266</v>
+        <v>-0.020285997345435562</v>
       </c>
       <c r="L5" s="0">
-        <v>0.013317843712922325</v>
+        <v>0.014010676486047884</v>
       </c>
       <c r="M5" s="0">
-        <v>0.00089378257010140107</v>
+        <v>-0.014932153510060739</v>
       </c>
       <c r="N5" s="0">
-        <v>0.46035404090630366</v>
+        <v>0.40877050092914163</v>
       </c>
       <c r="O5" s="0">
-        <v>0.0054403881157467325</v>
+        <v>0.011287878628934309</v>
       </c>
       <c r="P5" s="0">
-        <v>0.6554619331692626</v>
+        <v>0.64099775576842455</v>
       </c>
       <c r="Q5" s="0">
-        <v>-0.0086659995909133709</v>
+        <v>-0.01095339929057833</v>
       </c>
       <c r="R5" s="0">
-        <v>-9.2475011278424546</v>
+        <v>-15.211661771612979</v>
       </c>
       <c r="S5" s="0">
-        <v>0.0098489530899829314</v>
+        <v>0.0084358189305968161</v>
       </c>
       <c r="T5" s="0">
-        <v>0.020351607163679748</v>
+        <v>0.020895896045737765</v>
       </c>
       <c r="U5" s="0">
-        <v>0.02374220269828288</v>
+        <v>0.0071395089791679838</v>
       </c>
       <c r="V5" s="0">
-        <v>0.87457750324400285</v>
+        <v>0.8109801357056734</v>
       </c>
       <c r="W5" s="0">
-        <v>0.03962673466488334</v>
+        <v>0.044644730870603631</v>
       </c>
       <c r="X5" s="0">
-        <v>0.69664648106613325</v>
+        <v>0.68174853150750714</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.0077430031483182622</v>
+        <v>0.0052507874394466265</v>
       </c>
       <c r="Z5" s="0">
-        <v>-4.5812251423539392</v>
+        <v>-11.196075267361062</v>
       </c>
       <c r="AA5" s="0"/>
       <c r="AB5" s="0"/>
@@ -688,76 +688,76 @@
         <v>462</v>
       </c>
       <c r="C6" s="0">
-        <v>0.017453292519912098</v>
+        <v>0.017453292519912327</v>
       </c>
       <c r="D6" s="0">
-        <v>0.00027809164857527964</v>
+        <v>0.00025042647010875823</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.00062881877283743409</v>
+        <v>-0.00066797533530112488</v>
       </c>
       <c r="F6" s="0">
-        <v>0.83679130458748941</v>
+        <v>0.83691600331274096</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.020810227333077979</v>
+        <v>-0.020875704891956098</v>
       </c>
       <c r="H6" s="0">
-        <v>0.77712407628304647</v>
+        <v>0.77662861819782692</v>
       </c>
       <c r="I6" s="0">
-        <v>0.0049196817541785386</v>
+        <v>0.0048757385074176644</v>
       </c>
       <c r="J6" s="0">
-        <v>-2.6595821175685162</v>
+        <v>-2.8063393675470776</v>
       </c>
       <c r="K6" s="0">
-        <v>0.015593127973570346</v>
+        <v>0.015354403115616189</v>
       </c>
       <c r="L6" s="0">
-        <v>0.00015453470722375578</v>
+        <v>0.00011127311679209041</v>
       </c>
       <c r="M6" s="0">
-        <v>-0.00075224493349274274</v>
+        <v>-0.00080698241993267829</v>
       </c>
       <c r="N6" s="0">
-        <v>0.83292409434541315</v>
+        <v>0.83254724079316744</v>
       </c>
       <c r="O6" s="0">
-        <v>-0.021231938032324909</v>
+        <v>-0.021351394113637259</v>
       </c>
       <c r="P6" s="0">
-        <v>0.77249302144293874</v>
+        <v>0.77141406048432615</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.0045979205393013034</v>
+        <v>0.0045133752358200337</v>
       </c>
       <c r="R6" s="0">
-        <v>-2.6671494627768415</v>
+        <v>-2.814860884018159</v>
       </c>
       <c r="S6" s="0">
-        <v>0.019313457066253849</v>
+        <v>0.019552181924208465</v>
       </c>
       <c r="T6" s="0">
-        <v>0.00040164858992680348</v>
+        <v>0.00038957982342542608</v>
       </c>
       <c r="U6" s="0">
-        <v>-0.00050539261218212543</v>
+        <v>-0.00052896825066957147</v>
       </c>
       <c r="V6" s="0">
-        <v>0.84065851482956566</v>
+        <v>0.84128476583231449</v>
       </c>
       <c r="W6" s="0">
-        <v>-0.020388516633831049</v>
+        <v>-0.020400015670274937</v>
       </c>
       <c r="X6" s="0">
-        <v>0.7817551311231542</v>
+        <v>0.78184317591132768</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.0052414429690557738</v>
+        <v>0.0052381017790152952</v>
       </c>
       <c r="Z6" s="0">
-        <v>-2.6520147723601908</v>
+        <v>-2.7978178510759961</v>
       </c>
       <c r="AA6" s="0"/>
       <c r="AB6" s="0"/>
@@ -776,76 +776,76 @@
         <v>462</v>
       </c>
       <c r="C7" s="0">
-        <v>0.0010278580951742877</v>
+        <v>0.00099350919182524</v>
       </c>
       <c r="D7" s="0">
-        <v>0.0052504385227599443</v>
+        <v>0.0053168003151070386</v>
       </c>
       <c r="E7" s="0">
-        <v>0.0043701036758554352</v>
+        <v>0.0018059871307479823</v>
       </c>
       <c r="F7" s="0">
-        <v>0.79854806110585019</v>
+        <v>0.79624246972805124</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.01185021249090948</v>
+        <v>-0.011562093479785623</v>
       </c>
       <c r="H7" s="0">
-        <v>0.78684574138143615</v>
+        <v>0.78636598819296844</v>
       </c>
       <c r="I7" s="0">
-        <v>0.0038042399244939476</v>
+        <v>0.0037113811750797356</v>
       </c>
       <c r="J7" s="0">
-        <v>4.9016429495829117</v>
+        <v>4.5067524144920128</v>
       </c>
       <c r="K7" s="0">
-        <v>-0.0035321872687454829</v>
+        <v>-0.0034995976932567646</v>
       </c>
       <c r="L7" s="0">
-        <v>0.004075113079894453</v>
+        <v>0.0041589437665035794</v>
       </c>
       <c r="M7" s="0">
-        <v>0.00023324608656699174</v>
+        <v>-0.0022670591696319414</v>
       </c>
       <c r="N7" s="0">
-        <v>0.70279484075612408</v>
+        <v>0.70195711074540224</v>
       </c>
       <c r="O7" s="0">
-        <v>-0.018963397284384918</v>
+        <v>-0.018567758627370506</v>
       </c>
       <c r="P7" s="0">
-        <v>0.77899820646818863</v>
+        <v>0.7786378146958054</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.0015054088419306391</v>
+        <v>0.0014464274544618537</v>
       </c>
       <c r="R7" s="0">
-        <v>3.6690004109269374</v>
+        <v>3.2958372941252758</v>
       </c>
       <c r="S7" s="0">
-        <v>0.0055879034590940579</v>
+        <v>0.0054866160769072442</v>
       </c>
       <c r="T7" s="0">
-        <v>0.0064257639656254357</v>
+        <v>0.0064746568637104977</v>
       </c>
       <c r="U7" s="0">
-        <v>0.0085069612651438795</v>
+        <v>0.0058790334311279056</v>
       </c>
       <c r="V7" s="0">
-        <v>0.8943012814555763</v>
+        <v>0.89052782871070024</v>
       </c>
       <c r="W7" s="0">
-        <v>-0.0047370276974340441</v>
+        <v>-0.0045564283322007421</v>
       </c>
       <c r="X7" s="0">
-        <v>0.79469327629468367</v>
+        <v>0.79409416169013147</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.0061030710070572557</v>
+        <v>0.0059763348956976175</v>
       </c>
       <c r="Z7" s="0">
-        <v>6.134285488238886</v>
+        <v>5.7176675348587498</v>
       </c>
       <c r="AA7" s="0"/>
       <c r="AB7" s="0"/>
@@ -864,76 +864,76 @@
         <v>462</v>
       </c>
       <c r="C8" s="0">
-        <v>0.012288814410340307</v>
+        <v>0.011821392213191862</v>
       </c>
       <c r="D8" s="0">
-        <v>0.0068184693343833706</v>
+        <v>0.0069696265229651309</v>
       </c>
       <c r="E8" s="0">
-        <v>0.013539390923256244</v>
+        <v>0.011840475543559806</v>
       </c>
       <c r="F8" s="0">
-        <v>0.70023205153129609</v>
+        <v>0.69430868627470921</v>
       </c>
       <c r="G8" s="0">
-        <v>-0.0052795791675551256</v>
+        <v>-0.0045551790062475072</v>
       </c>
       <c r="H8" s="0">
-        <v>0.78888207455326687</v>
+        <v>0.78782885527645019</v>
       </c>
       <c r="I8" s="0">
-        <v>0.012731609799617018</v>
+        <v>0.012412882815204071</v>
       </c>
       <c r="J8" s="0">
-        <v>0.32476189072459311</v>
+        <v>-0.57308866222807153</v>
       </c>
       <c r="K8" s="0">
-        <v>0.0068653386234190173</v>
+        <v>0.0069821049097160675</v>
       </c>
       <c r="L8" s="0">
-        <v>0.0050697949972054752</v>
+        <v>0.0054119345832602493</v>
       </c>
       <c r="M8" s="0">
-        <v>0.0088597373184038323</v>
+        <v>0.0076632682275419679</v>
       </c>
       <c r="N8" s="0">
-        <v>0.58947431960157681</v>
+        <v>0.59565988960854199</v>
       </c>
       <c r="O8" s="0">
-        <v>-0.013672377264492046</v>
+        <v>-0.012031181510126922</v>
       </c>
       <c r="P8" s="0">
-        <v>0.78032036836952024</v>
+        <v>0.78020212320634252</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.0088250888824111598</v>
+        <v>0.0089302856590868333</v>
       </c>
       <c r="R8" s="0">
-        <v>-0.55099473692920853</v>
+        <v>-1.345842289879879</v>
       </c>
       <c r="S8" s="0">
-        <v>0.017712290197261598</v>
+        <v>0.016660679516667658</v>
       </c>
       <c r="T8" s="0">
-        <v>0.008567143671561266</v>
+        <v>0.0085273184626700124</v>
       </c>
       <c r="U8" s="0">
-        <v>0.018219044528108658</v>
+        <v>0.016017682859577644</v>
       </c>
       <c r="V8" s="0">
-        <v>0.81098978346101536</v>
+        <v>0.79295748294087642</v>
       </c>
       <c r="W8" s="0">
-        <v>0.0031132189293817947</v>
+        <v>0.0029208234976319074</v>
       </c>
       <c r="X8" s="0">
-        <v>0.7974437807370135</v>
+        <v>0.79545558734655786</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.016638130716822876</v>
+        <v>0.015895479971321309</v>
       </c>
       <c r="Z8" s="0">
-        <v>1.2005185183783946</v>
+        <v>0.19966496542373602</v>
       </c>
       <c r="AA8" s="0"/>
       <c r="AB8" s="0"/>
@@ -949,79 +949,79 @@
         <v>3</v>
       </c>
       <c r="B9" s="0">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C9" s="0">
-        <v>0.0049294823343776885</v>
+        <v>0.0049258171301324698</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.0038546559738495026</v>
+        <v>-0.0038544032179176615</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.00057437811787119551</v>
+        <v>-0.00057491979987727804</v>
       </c>
       <c r="F9" s="0">
-        <v>0.72006212692952332</v>
+        <v>0.71995959202913651</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.024522033012010145</v>
+        <v>-0.024511341510303798</v>
       </c>
       <c r="H9" s="0">
-        <v>0.7792062865859154</v>
+        <v>0.77920178680589758</v>
       </c>
       <c r="I9" s="0">
-        <v>0.0077294229362769723</v>
+        <v>0.0077298578694328839</v>
       </c>
       <c r="J9" s="0">
-        <v>-2.5460942727930274</v>
+        <v>-2.8747767518717953</v>
       </c>
       <c r="K9" s="0">
-        <v>0.0017956868871125886</v>
+        <v>0.0018042688993567813</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.0040304021949728866</v>
+        <v>-0.0040293921958705755</v>
       </c>
       <c r="M9" s="0">
-        <v>-0.00075476793468289547</v>
+        <v>-0.00075452489022338916</v>
       </c>
       <c r="N9" s="0">
-        <v>0.69783996833225526</v>
+        <v>0.69783107142473488</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.026786880994326755</v>
+        <v>-0.026766687837091633</v>
       </c>
       <c r="P9" s="0">
-        <v>0.77442636750031169</v>
+        <v>0.77444100422956075</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.007257888612882883</v>
+        <v>0.0072602225861206141</v>
       </c>
       <c r="R9" s="0">
-        <v>-2.5586444327153863</v>
+        <v>-2.8872730801377404</v>
       </c>
       <c r="S9" s="0">
-        <v>0.0080632777816427893</v>
+        <v>0.0080473653609081583</v>
       </c>
       <c r="T9" s="0">
-        <v>-0.0036789097527261186</v>
+        <v>-0.0036794142399647479</v>
       </c>
       <c r="U9" s="0">
-        <v>-0.00039398830105949549</v>
+        <v>-0.00039531470953116691</v>
       </c>
       <c r="V9" s="0">
-        <v>0.74228428552679138</v>
+        <v>0.74208811263353813</v>
       </c>
       <c r="W9" s="0">
-        <v>-0.022257185029693535</v>
+        <v>-0.022255995183515964</v>
       </c>
       <c r="X9" s="0">
-        <v>0.78398620567151911</v>
+        <v>0.78396256938223441</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.0082009572596710625</v>
+        <v>0.0081994931527451537</v>
       </c>
       <c r="Z9" s="0">
-        <v>-2.5335441128706684</v>
+        <v>-2.8622804236058501</v>
       </c>
       <c r="AA9" s="0"/>
       <c r="AB9" s="0"/>
@@ -1037,79 +1037,79 @@
         <v>3</v>
       </c>
       <c r="B10" s="0">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C10" s="0">
-        <v>0.017453062827398311</v>
+        <v>0.017453214541719136</v>
       </c>
       <c r="D10" s="0">
-        <v>0.00032534118956346767</v>
+        <v>0.00028580742253769858</v>
       </c>
       <c r="E10" s="0">
-        <v>0.0006609445701649412</v>
+        <v>0.00066689807807165881</v>
       </c>
       <c r="F10" s="0">
-        <v>0.74527824047804259</v>
+        <v>0.74693070862199351</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.017697053563691903</v>
+        <v>-0.017969707081091677</v>
       </c>
       <c r="H10" s="0">
-        <v>0.81016317724094522</v>
+        <v>0.80445381636935798</v>
       </c>
       <c r="I10" s="0">
-        <v>0.0068696040708020748</v>
+        <v>0.0068030165277586253</v>
       </c>
       <c r="J10" s="0">
-        <v>-2.254110139666027</v>
+        <v>-2.4984202471553299</v>
       </c>
       <c r="K10" s="0">
-        <v>0.015062909154127181</v>
+        <v>0.014982830829762307</v>
       </c>
       <c r="L10" s="0">
-        <v>0.00020579103130151223</v>
+        <v>0.00016236214967625703</v>
       </c>
       <c r="M10" s="0">
-        <v>0.00054269098538922342</v>
+        <v>0.00054477704620885183</v>
       </c>
       <c r="N10" s="0">
-        <v>0.7415028553156181</v>
+        <v>0.74303201522734708</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.018211058075908546</v>
+        <v>-0.018500399412656105</v>
       </c>
       <c r="P10" s="0">
-        <v>0.8034834317666546</v>
+        <v>0.79755648830834858</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.0064196590554763773</v>
+        <v>0.0063383394928987784</v>
       </c>
       <c r="R10" s="0">
-        <v>-2.259893730313737</v>
+        <v>-2.5043918381970571</v>
       </c>
       <c r="S10" s="0">
-        <v>0.01984321650066944</v>
+        <v>0.019923598253675966</v>
       </c>
       <c r="T10" s="0">
-        <v>0.00044489134782542308</v>
+        <v>0.0004092526953991401</v>
       </c>
       <c r="U10" s="0">
-        <v>0.00077919815494065898</v>
+        <v>0.00078901910993446579</v>
       </c>
       <c r="V10" s="0">
-        <v>0.74905362564046707</v>
+        <v>0.75082940201663995</v>
       </c>
       <c r="W10" s="0">
-        <v>-0.017183049051475261</v>
+        <v>-0.017439014749527249</v>
       </c>
       <c r="X10" s="0">
-        <v>0.81684292271523584</v>
+        <v>0.81135114443036738</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.0073195490861277723</v>
+        <v>0.0072676935626184722</v>
       </c>
       <c r="Z10" s="0">
-        <v>-2.2483265490183171</v>
+        <v>-2.4924486561136026</v>
       </c>
       <c r="AA10" s="0"/>
       <c r="AB10" s="0"/>
@@ -1125,79 +1125,79 @@
         <v>3</v>
       </c>
       <c r="B11" s="0">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C11" s="0">
-        <v>0.0083836924300078122</v>
+        <v>0.0055231915203429851</v>
       </c>
       <c r="D11" s="0">
-        <v>0.002076286916131325</v>
+        <v>0.0011437390022331136</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.034906299629696269</v>
+        <v>-0.034906579164167867</v>
       </c>
       <c r="F11" s="0">
-        <v>0.6492925557576833</v>
+        <v>0.6475330092452013</v>
       </c>
       <c r="G11" s="0">
-        <v>-0.0047402659366508424</v>
+        <v>-0.0063070305763054538</v>
       </c>
       <c r="H11" s="0">
-        <v>0.7867464484381691</v>
+        <v>0.78534233610755266</v>
       </c>
       <c r="I11" s="0">
-        <v>0.011529530704221289</v>
+        <v>0.0061790265758804403</v>
       </c>
       <c r="J11" s="0">
-        <v>-4.1912194018938633</v>
+        <v>-7.4264747146110022</v>
       </c>
       <c r="K11" s="0">
-        <v>0.00033335756796099361</v>
+        <v>-0.0020235410469055439</v>
       </c>
       <c r="L11" s="0">
-        <v>-0.0015424400421587621</v>
+        <v>-0.0022442828449826197</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.04423885012740475</v>
+        <v>-0.043768117574256416</v>
       </c>
       <c r="N11" s="0">
-        <v>0.55293928583622987</v>
+        <v>0.55732446293337001</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.015488849814418818</v>
+        <v>-0.016357947838635836</v>
       </c>
       <c r="P11" s="0">
-        <v>0.77440368676014082</v>
+        <v>0.77378151396054828</v>
       </c>
       <c r="Q11" s="0">
-        <v>0.0037917687324036829</v>
+        <v>-0.0010402617857876908</v>
       </c>
       <c r="R11" s="0">
-        <v>-5.6210264092675786</v>
+        <v>-8.6926613256162124</v>
       </c>
       <c r="S11" s="0">
-        <v>0.016434027292054631</v>
+        <v>0.013069924087591514</v>
       </c>
       <c r="T11" s="0">
-        <v>0.0056950138744214125</v>
+        <v>0.0045317608494488465</v>
       </c>
       <c r="U11" s="0">
-        <v>-0.025573749131987792</v>
+        <v>-0.026045040754079315</v>
       </c>
       <c r="V11" s="0">
-        <v>0.74564582567913673</v>
+        <v>0.73774155555703258</v>
       </c>
       <c r="W11" s="0">
-        <v>0.006008317941117133</v>
+        <v>0.0037438866860249271</v>
       </c>
       <c r="X11" s="0">
-        <v>0.79908921011619738</v>
+        <v>0.79690315825455704</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.019267292676038893</v>
+        <v>0.013398314937548571</v>
       </c>
       <c r="Z11" s="0">
-        <v>-2.7614123945201481</v>
+        <v>-6.1602881036057919</v>
       </c>
       <c r="AA11" s="0"/>
       <c r="AB11" s="0"/>
@@ -1216,76 +1216,76 @@
         <v>462</v>
       </c>
       <c r="C12" s="0">
-        <v>0.01745305517339997</v>
+        <v>0.017452869591898477</v>
       </c>
       <c r="D12" s="0">
-        <v>0.0046848932904817202</v>
+        <v>0.0046856574195044973</v>
       </c>
       <c r="E12" s="0">
-        <v>0.0015013170715910704</v>
+        <v>0.0015037535581509894</v>
       </c>
       <c r="F12" s="0">
-        <v>0.86075898160345377</v>
+        <v>0.86063595578249052</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.019600030481600025</v>
+        <v>-0.019587083876224202</v>
       </c>
       <c r="H12" s="0">
-        <v>0.76685599261065984</v>
+        <v>0.76689888349996005</v>
       </c>
       <c r="I12" s="0">
-        <v>0.0056681993134317299</v>
+        <v>0.0056633754160928919</v>
       </c>
       <c r="J12" s="0">
-        <v>-2.4532826486946644</v>
+        <v>-2.7754234156215225</v>
       </c>
       <c r="K12" s="0">
-        <v>0.013727821934431275</v>
+        <v>0.013749315854790117</v>
       </c>
       <c r="L12" s="0">
-        <v>0.0044467604739314827</v>
+        <v>0.0044489509926803929</v>
       </c>
       <c r="M12" s="0">
-        <v>0.0012603153338210697</v>
+        <v>0.0012642042351745353</v>
       </c>
       <c r="N12" s="0">
-        <v>0.84120706472409279</v>
+        <v>0.84120305718775779</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.021699622205759064</v>
+        <v>-0.021674025419301281</v>
       </c>
       <c r="P12" s="0">
-        <v>0.76088123629476001</v>
+        <v>0.76095852543283615</v>
       </c>
       <c r="Q12" s="0">
-        <v>0.0049188857410360958</v>
+        <v>0.0049184406080036601</v>
       </c>
       <c r="R12" s="0">
-        <v>-2.4694321245863824</v>
+        <v>-2.7914764509969747</v>
       </c>
       <c r="S12" s="0">
-        <v>0.021178288412368663</v>
+        <v>0.021156423329006836</v>
       </c>
       <c r="T12" s="0">
-        <v>0.0049230261070319576</v>
+        <v>0.0049223638463286017</v>
       </c>
       <c r="U12" s="0">
-        <v>0.0017423188093610711</v>
+        <v>0.0017433028811274435</v>
       </c>
       <c r="V12" s="0">
-        <v>0.88031089848281474</v>
+        <v>0.88006885437722327</v>
       </c>
       <c r="W12" s="0">
-        <v>-0.017500438757440985</v>
+        <v>-0.017500142333147124</v>
       </c>
       <c r="X12" s="0">
-        <v>0.77283074892655967</v>
+        <v>0.77283924156708395</v>
       </c>
       <c r="Y12" s="0">
-        <v>0.0064175128858273639</v>
+        <v>0.0064083102241821238</v>
       </c>
       <c r="Z12" s="0">
-        <v>-2.4371331728029464</v>
+        <v>-2.7593703802460703</v>
       </c>
       <c r="AA12" s="0"/>
       <c r="AB12" s="0"/>
@@ -1304,76 +1304,76 @@
         <v>462</v>
       </c>
       <c r="C13" s="0">
-        <v>0.0059293932258079399</v>
+        <v>0.0068405878517542934</v>
       </c>
       <c r="D13" s="0">
-        <v>0.0021447171031506269</v>
+        <v>0.0020917346998750299</v>
       </c>
       <c r="E13" s="0">
-        <v>0.0013379236269897489</v>
+        <v>0.0013420352317811354</v>
       </c>
       <c r="F13" s="0">
-        <v>0.85464513404652143</v>
+        <v>0.85676651632558132</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.026059670277124018</v>
+        <v>-0.026411588157698538</v>
       </c>
       <c r="H13" s="0">
-        <v>0.76347824522548735</v>
+        <v>0.7572457249436525</v>
       </c>
       <c r="I13" s="0">
-        <v>0.0016029421132122575</v>
+        <v>0.0016962172031619038</v>
       </c>
       <c r="J13" s="0">
-        <v>-2.2498716285888949</v>
+        <v>-2.4587343977604004</v>
       </c>
       <c r="K13" s="0">
-        <v>0.0012643181108731834</v>
+        <v>0.0020198629691279158</v>
       </c>
       <c r="L13" s="0">
-        <v>0.0019286537190288148</v>
+        <v>0.0018682824998264077</v>
       </c>
       <c r="M13" s="0">
-        <v>0.0011280175941366685</v>
+        <v>0.0011249329356879648</v>
       </c>
       <c r="N13" s="0">
-        <v>0.84757101910743515</v>
+        <v>0.84945223921376767</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.027049960345377308</v>
+        <v>-0.027435027952280988</v>
       </c>
       <c r="P13" s="0">
-        <v>0.74801753424269957</v>
+        <v>0.7412723272226931</v>
       </c>
       <c r="Q13" s="0">
-        <v>0.00068330924218769459</v>
+        <v>0.0007465476503644155</v>
       </c>
       <c r="R13" s="0">
-        <v>-2.2609872110124476</v>
+        <v>-2.4702284242250414</v>
       </c>
       <c r="S13" s="0">
-        <v>0.010594468340742697</v>
+        <v>0.011661312734380671</v>
       </c>
       <c r="T13" s="0">
-        <v>0.0023607804872724392</v>
+        <v>0.002315186899923652</v>
       </c>
       <c r="U13" s="0">
-        <v>0.0015478296598428294</v>
+        <v>0.0015591375278743061</v>
       </c>
       <c r="V13" s="0">
-        <v>0.8617192489856077</v>
+        <v>0.86408079343739497</v>
       </c>
       <c r="W13" s="0">
-        <v>-0.025069380208870729</v>
+        <v>-0.025388148363116089</v>
       </c>
       <c r="X13" s="0">
-        <v>0.77893895620827514</v>
+        <v>0.7732191226646119</v>
       </c>
       <c r="Y13" s="0">
-        <v>0.0025225749842368202</v>
+        <v>0.0026458867559593924</v>
       </c>
       <c r="Z13" s="0">
-        <v>-2.2387560461653422</v>
+        <v>-2.4472403712957593</v>
       </c>
       <c r="AA13" s="0"/>
       <c r="AB13" s="0"/>
@@ -1392,76 +1392,76 @@
         <v>462</v>
       </c>
       <c r="C14" s="0">
-        <v>0.017453292509990673</v>
+        <v>0.017453292508293222</v>
       </c>
       <c r="D14" s="0">
-        <v>0.0086898908493166296</v>
+        <v>0.008751766503761348</v>
       </c>
       <c r="E14" s="0">
-        <v>0.00018636219735431293</v>
+        <v>0.00022991701878918877</v>
       </c>
       <c r="F14" s="0">
-        <v>0.73780267991474735</v>
+        <v>0.73776127864978247</v>
       </c>
       <c r="G14" s="0">
-        <v>0.0012129845636887214</v>
+        <v>0.0013409820967055694</v>
       </c>
       <c r="H14" s="0">
-        <v>0.98375728122116524</v>
+        <v>0.98734794113833169</v>
       </c>
       <c r="I14" s="0">
-        <v>0.0093706965611656274</v>
+        <v>0.009400975016218574</v>
       </c>
       <c r="J14" s="0">
-        <v>-1.7015658840123766</v>
+        <v>-1.8978970753182045</v>
       </c>
       <c r="K14" s="0">
-        <v>0.0093802733883478814</v>
+        <v>0.0091802900573087036</v>
       </c>
       <c r="L14" s="0">
-        <v>0.0074675770129922301</v>
+        <v>0.0074997239963722822</v>
       </c>
       <c r="M14" s="0">
-        <v>-0.0010279844675760296</v>
+        <v>-0.0010141251460039466</v>
       </c>
       <c r="N14" s="0">
-        <v>0.72454533824344802</v>
+        <v>0.72416782467968444</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.0015874699360873515</v>
+        <v>-0.0015281826343785079</v>
       </c>
       <c r="P14" s="0">
-        <v>0.94900848243319447</v>
+        <v>0.9517288661987342</v>
       </c>
       <c r="Q14" s="0">
-        <v>0.0067677307131187858</v>
+        <v>0.0067336932075331857</v>
       </c>
       <c r="R14" s="0">
-        <v>-1.7417428528460779</v>
+        <v>-1.939087237803502</v>
       </c>
       <c r="S14" s="0">
-        <v>0.025526311631633464</v>
+        <v>0.025726294959277741</v>
       </c>
       <c r="T14" s="0">
-        <v>0.0099122046856410292</v>
+        <v>0.010003809011150415</v>
       </c>
       <c r="U14" s="0">
-        <v>0.0014007088622846552</v>
+        <v>0.0014739591835823242</v>
       </c>
       <c r="V14" s="0">
-        <v>0.75106002158604668</v>
+        <v>0.75135473261988051</v>
       </c>
       <c r="W14" s="0">
-        <v>0.0040134390634647948</v>
+        <v>0.0042101468277896473</v>
       </c>
       <c r="X14" s="0">
-        <v>1.0185060800091359</v>
+        <v>1.0229670160779292</v>
       </c>
       <c r="Y14" s="0">
-        <v>0.011973662409212469</v>
+        <v>0.012068256824903962</v>
       </c>
       <c r="Z14" s="0">
-        <v>-1.6613889151786754</v>
+        <v>-1.856706912832907</v>
       </c>
       <c r="AA14" s="0"/>
       <c r="AB14" s="0"/>
@@ -1480,76 +1480,76 @@
         <v>462</v>
       </c>
       <c r="C15" s="0">
-        <v>0.0066863609243270894</v>
+        <v>0.0066762516769858261</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.017453292519092802</v>
+        <v>-0.017453292519347723</v>
       </c>
       <c r="E15" s="0">
-        <v>-0.0015212601146836085</v>
+        <v>-0.0022922571573304753</v>
       </c>
       <c r="F15" s="0">
-        <v>0.76145048996755227</v>
+        <v>0.76139646069525813</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.051911128643372384</v>
+        <v>-0.051904854459423069</v>
       </c>
       <c r="H15" s="0">
-        <v>0.79952225706923252</v>
+        <v>0.79949332764238956</v>
       </c>
       <c r="I15" s="0">
-        <v>0.011787548345596316</v>
+        <v>0.011773452026456134</v>
       </c>
       <c r="J15" s="0">
-        <v>1.053016251307866</v>
+        <v>0.8431021088400571</v>
       </c>
       <c r="K15" s="0">
-        <v>0.002478631636432329</v>
+        <v>0.0024648145381359881</v>
       </c>
       <c r="L15" s="0">
-        <v>-0.019954005140709535</v>
+        <v>-0.019955268230839117</v>
       </c>
       <c r="M15" s="0">
-        <v>-0.008353906791460473</v>
+        <v>-0.009117139807196542</v>
       </c>
       <c r="N15" s="0">
-        <v>0.69733305263909873</v>
+        <v>0.6972347761470149</v>
       </c>
       <c r="O15" s="0">
-        <v>-0.059662223148644528</v>
+        <v>-0.059660875175406608</v>
       </c>
       <c r="P15" s="0">
-        <v>0.79254836178600507</v>
+        <v>0.792520076482498</v>
       </c>
       <c r="Q15" s="0">
-        <v>0.0067783718009484959</v>
+        <v>0.0067620379462914743</v>
       </c>
       <c r="R15" s="0">
-        <v>0.020983323021948053</v>
+        <v>-0.19061572442177377</v>
       </c>
       <c r="S15" s="0">
-        <v>0.01089409021222185</v>
+        <v>0.010887688815835664</v>
       </c>
       <c r="T15" s="0">
-        <v>-0.01495257989747607</v>
+        <v>-0.014951316807856331</v>
       </c>
       <c r="U15" s="0">
-        <v>0.0053113865620932552</v>
+        <v>0.0045326254925355924</v>
       </c>
       <c r="V15" s="0">
-        <v>0.82556792729600581</v>
+        <v>0.82555814524350135</v>
       </c>
       <c r="W15" s="0">
-        <v>-0.04416003413810024</v>
+        <v>-0.044148833743439531</v>
       </c>
       <c r="X15" s="0">
-        <v>0.80649615235245997</v>
+        <v>0.80646657880228112</v>
       </c>
       <c r="Y15" s="0">
-        <v>0.016796724890244134</v>
+        <v>0.016784866106620795</v>
       </c>
       <c r="Z15" s="0">
-        <v>2.085049179593784</v>
+        <v>1.8768199421018879</v>
       </c>
       <c r="AA15" s="0"/>
       <c r="AB15" s="0"/>
@@ -1568,76 +1568,76 @@
         <v>462</v>
       </c>
       <c r="C16" s="0">
-        <v>0.013590960572112423</v>
+        <v>0.013594223424030777</v>
       </c>
       <c r="D16" s="0">
-        <v>0.00031133038832832503</v>
+        <v>0.00031170175900958674</v>
       </c>
       <c r="E16" s="0">
-        <v>-5.6037777119985108e-05</v>
+        <v>-6.1266833770603265e-05</v>
       </c>
       <c r="F16" s="0">
-        <v>0.69966281258064744</v>
+        <v>0.69973828651635417</v>
       </c>
       <c r="G16" s="0">
-        <v>-0.010931965346342014</v>
+        <v>-0.010938296637353314</v>
       </c>
       <c r="H16" s="0">
-        <v>0.78742864407039836</v>
+        <v>0.78741749370107583</v>
       </c>
       <c r="I16" s="0">
-        <v>0.011555462483675132</v>
+        <v>0.011556258343557198</v>
       </c>
       <c r="J16" s="0">
-        <v>-2.6264725803804212</v>
+        <v>-3.0597970257156533</v>
       </c>
       <c r="K16" s="0">
-        <v>0.0097394101854487679</v>
+        <v>0.0097320602362613463</v>
       </c>
       <c r="L16" s="0">
-        <v>1.52784539276951e-05</v>
+        <v>1.4925541380792081e-05</v>
       </c>
       <c r="M16" s="0">
-        <v>-0.00035463691869899977</v>
+        <v>-0.00036059562452148619</v>
       </c>
       <c r="N16" s="0">
-        <v>0.66495016517453309</v>
+        <v>0.66494324269897387</v>
       </c>
       <c r="O16" s="0">
-        <v>-0.014112204966983604</v>
+        <v>-0.014126230535837479</v>
       </c>
       <c r="P16" s="0">
-        <v>0.781270791718506</v>
+        <v>0.78124271216721641</v>
       </c>
       <c r="Q16" s="0">
-        <v>0.010811712084108756</v>
+        <v>0.010810561332483126</v>
       </c>
       <c r="R16" s="0">
-        <v>-2.6494769232063709</v>
+        <v>-3.082858829254544</v>
       </c>
       <c r="S16" s="0">
-        <v>0.017442510958776077</v>
+        <v>0.017456386611800209</v>
       </c>
       <c r="T16" s="0">
-        <v>0.00060738232272895495</v>
+        <v>0.00060847797663838134</v>
       </c>
       <c r="U16" s="0">
-        <v>0.00024256136445902955</v>
+        <v>0.00023806195698027966</v>
       </c>
       <c r="V16" s="0">
-        <v>0.73437545998676179</v>
+        <v>0.73453333033373447</v>
       </c>
       <c r="W16" s="0">
-        <v>-0.0077517257257004244</v>
+        <v>-0.0077503627388691501</v>
       </c>
       <c r="X16" s="0">
-        <v>0.79358649642229073</v>
+        <v>0.79359227523493525</v>
       </c>
       <c r="Y16" s="0">
-        <v>0.012299212883241508</v>
+        <v>0.01230195535463127</v>
       </c>
       <c r="Z16" s="0">
-        <v>-2.6034682375544716</v>
+        <v>-3.0367352221767625</v>
       </c>
       <c r="AA16" s="0"/>
       <c r="AB16" s="0"/>
@@ -1656,76 +1656,76 @@
         <v>462</v>
       </c>
       <c r="C17" s="0">
-        <v>0.017453289943470052</v>
+        <v>0.017453289909113556</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.0043211321753232864</v>
+        <v>-0.0043350694919015095</v>
       </c>
       <c r="E17" s="0">
-        <v>0.0026765517776769772</v>
+        <v>0.0026975557140245755</v>
       </c>
       <c r="F17" s="0">
-        <v>0.75007396344564792</v>
+        <v>0.75142974931479101</v>
       </c>
       <c r="G17" s="0">
-        <v>-0.025739888383358448</v>
+        <v>-0.025897088683332393</v>
       </c>
       <c r="H17" s="0">
-        <v>0.60931946813829863</v>
+        <v>0.60584156187762106</v>
       </c>
       <c r="I17" s="0">
-        <v>0.0026516976666205458</v>
+        <v>0.0025901243068570134</v>
       </c>
       <c r="J17" s="0">
-        <v>-2.5293731459450539</v>
+        <v>-2.8828237943878978</v>
       </c>
       <c r="K17" s="0">
-        <v>0.013866169687344002</v>
+        <v>0.013298070277988959</v>
       </c>
       <c r="L17" s="0">
-        <v>-0.0045100438999039674</v>
+        <v>-0.0045541383174920527</v>
       </c>
       <c r="M17" s="0">
-        <v>0.0024917171311663634</v>
+        <v>0.0024832050164074367</v>
       </c>
       <c r="N17" s="0">
-        <v>0.74480845760674985</v>
+        <v>0.74532159250028662</v>
       </c>
       <c r="O17" s="0">
-        <v>-0.026371166934604468</v>
+        <v>-0.026628918456070259</v>
       </c>
       <c r="P17" s="0">
-        <v>0.59525912295097905</v>
+        <v>0.58952817467952989</v>
       </c>
       <c r="Q17" s="0">
-        <v>0.0021002945315948423</v>
+        <v>0.0019513589067345887</v>
       </c>
       <c r="R17" s="0">
-        <v>-2.5402420411811022</v>
+        <v>-2.8954194622451115</v>
       </c>
       <c r="S17" s="0">
-        <v>0.021040410199596103</v>
+        <v>0.021608509540238151</v>
       </c>
       <c r="T17" s="0">
-        <v>-0.0041322204507426054</v>
+        <v>-0.0041160006663109663</v>
       </c>
       <c r="U17" s="0">
-        <v>0.0028613864241875909</v>
+        <v>0.0029119064116417143</v>
       </c>
       <c r="V17" s="0">
-        <v>0.75533946928454598</v>
+        <v>0.75753790612929539</v>
       </c>
       <c r="W17" s="0">
-        <v>-0.025108609832112428</v>
+        <v>-0.025165258910594526</v>
       </c>
       <c r="X17" s="0">
-        <v>0.6233798133256182</v>
+        <v>0.62215494907571223</v>
       </c>
       <c r="Y17" s="0">
-        <v>0.0032031008016462493</v>
+        <v>0.0032288897069794381</v>
       </c>
       <c r="Z17" s="0">
-        <v>-2.5185042507090056</v>
+        <v>-2.8702281265306842</v>
       </c>
       <c r="AA17" s="0"/>
       <c r="AB17" s="0"/>
@@ -1744,76 +1744,76 @@
         <v>462</v>
       </c>
       <c r="C18" s="0">
-        <v>0.0020057457879243054</v>
+        <v>0.00058317908956743167</v>
       </c>
       <c r="D18" s="0">
-        <v>-0.0066963541575014683</v>
+        <v>-0.0068380403781858968</v>
       </c>
       <c r="E18" s="0">
-        <v>-0.0014733219768185222</v>
+        <v>-0.001470552753801939</v>
       </c>
       <c r="F18" s="0">
-        <v>0.83148290890679788</v>
+        <v>0.84014289801080888</v>
       </c>
       <c r="G18" s="0">
-        <v>-0.036473168711246791</v>
+        <v>-0.037559925965762901</v>
       </c>
       <c r="H18" s="0">
-        <v>0.7074047538114272</v>
+        <v>0.69429716289422827</v>
       </c>
       <c r="I18" s="0">
-        <v>0.0083012122996640164</v>
+        <v>0.0080663898257326023</v>
       </c>
       <c r="J18" s="0">
-        <v>-2.4203872565552938</v>
+        <v>-2.7790663730444099</v>
       </c>
       <c r="K18" s="0">
-        <v>-0.0024935787026979699</v>
+        <v>-0.0043522432372722283</v>
       </c>
       <c r="L18" s="0">
-        <v>-0.0068936968957802793</v>
+        <v>-0.0070560553529360279</v>
       </c>
       <c r="M18" s="0">
-        <v>-0.0016621132184515704</v>
+        <v>-0.0016790379754966266</v>
       </c>
       <c r="N18" s="0">
-        <v>0.82604760442376068</v>
+        <v>0.8341422157395364</v>
       </c>
       <c r="O18" s="0">
-        <v>-0.037127189849049072</v>
+        <v>-0.038281639763851183</v>
       </c>
       <c r="P18" s="0">
-        <v>0.68614255192991891</v>
+        <v>0.67075987924044467</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.0076307644919752964</v>
+        <v>0.0073300069875887374</v>
       </c>
       <c r="R18" s="0">
-        <v>-2.4333545216182553</v>
+        <v>-2.7933814832591621</v>
       </c>
       <c r="S18" s="0">
-        <v>0.0065050702785465807</v>
+        <v>0.0055186014164070908</v>
       </c>
       <c r="T18" s="0">
-        <v>-0.0064990114192226573</v>
+        <v>-0.0066200254034357656</v>
       </c>
       <c r="U18" s="0">
-        <v>-0.001284530735185474</v>
+        <v>-0.0012620675321072515</v>
       </c>
       <c r="V18" s="0">
-        <v>0.83691821338983508</v>
+        <v>0.84614358028208137</v>
       </c>
       <c r="W18" s="0">
-        <v>-0.03581914757344451</v>
+        <v>-0.036838212167674619</v>
       </c>
       <c r="X18" s="0">
-        <v>0.72866695569293549</v>
+        <v>0.71783444654801187</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.0089716601073527372</v>
+        <v>0.0088027726638764663</v>
       </c>
       <c r="Z18" s="0">
-        <v>-2.4074199914923322</v>
+        <v>-2.7647512628296576</v>
       </c>
       <c r="AA18" s="0"/>
       <c r="AB18" s="0"/>
@@ -1866,76 +1866,76 @@
       </c>
       <c r="B20" s="0"/>
       <c r="C20" s="0">
-        <v>0.010603987995925398</v>
+        <v>0.010305792074629502</v>
       </c>
       <c r="D20" s="0">
-        <v>0.0018371605840431921</v>
+        <v>0.0019045370582384685</v>
       </c>
       <c r="E20" s="0">
-        <v>0.001060999041204151</v>
+        <v>-6.0042121520166528e-05</v>
       </c>
       <c r="F20" s="0">
-        <v>0.71816980169330757</v>
+        <v>0.71579520068372138</v>
       </c>
       <c r="G20" s="0">
-        <v>-0.013378863011054828</v>
+        <v>-0.011587470298316357</v>
       </c>
       <c r="H20" s="0">
-        <v>0.73668906581123284</v>
+        <v>0.73161796231967113</v>
       </c>
       <c r="I20" s="0">
-        <v>0.0060269843665620168</v>
+        <v>0.0081794996300656626</v>
       </c>
       <c r="J20" s="0">
-        <v>-2.348994905526661</v>
+        <v>-3.1751560210327612</v>
       </c>
       <c r="K20" s="0">
-        <v>0.0055486957614623829</v>
+        <v>0.0063990054528077576</v>
       </c>
       <c r="L20" s="0">
-        <v>0.0010248841284185752</v>
+        <v>0.001064920434537379</v>
       </c>
       <c r="M20" s="0">
-        <v>-0.0013133611067037622</v>
+        <v>-0.0024314570205388368</v>
       </c>
       <c r="N20" s="0">
-        <v>0.67169181601507211</v>
+        <v>0.78858608593121127</v>
       </c>
       <c r="O20" s="0">
-        <v>-0.017207353687568382</v>
+        <v>-0.0074683007876797727</v>
       </c>
       <c r="P20" s="0">
-        <v>0.72270560131880624</v>
+        <v>0.73128649284734637</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.0039324022588973538</v>
+        <v>0.0063855905314056998</v>
       </c>
       <c r="R20" s="0">
-        <v>-2.7860680104170941</v>
+        <v>-3.5598672096573729</v>
       </c>
       <c r="S20" s="0">
-        <v>0.015141116557368186</v>
+        <v>0.016533669826080153</v>
       </c>
       <c r="T20" s="0">
-        <v>0.0027732089591284868</v>
+        <v>0.00295629334854216</v>
       </c>
       <c r="U20" s="0">
-        <v>0.003464945204404732</v>
+        <v>0.0023957796130437137</v>
       </c>
       <c r="V20" s="0">
-        <v>0.76059815312514167</v>
+        <v>0.88960683969632082</v>
       </c>
       <c r="W20" s="0">
-        <v>-0.0092662969026032233</v>
+        <v>0.00052297569920850843</v>
       </c>
       <c r="X20" s="0">
-        <v>0.74796150851116328</v>
+        <v>0.76130328214356768</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.0081317120897631858</v>
+        <v>0.010334478596827708</v>
       </c>
       <c r="Z20" s="0">
-        <v>-1.9129649308124648</v>
+        <v>-2.772748795996506</v>
       </c>
       <c r="AA20" s="0"/>
       <c r="AB20" s="0"/>
@@ -1952,76 +1952,76 @@
       </c>
       <c r="B21" s="0"/>
       <c r="C21" s="0">
-        <v>0.0069042906183865585</v>
+        <v>0.0072178244253886187</v>
       </c>
       <c r="D21" s="0">
-        <v>0.0078238639865113608</v>
+        <v>0.0079461574068782799</v>
       </c>
       <c r="E21" s="0">
-        <v>0.010008767751482562</v>
+        <v>0.0094313764628704173</v>
       </c>
       <c r="F21" s="0">
-        <v>0.15125938223127516</v>
+        <v>0.14949318969687731</v>
       </c>
       <c r="G21" s="0">
-        <v>0.019978406513714048</v>
+        <v>0.024121339178633874</v>
       </c>
       <c r="H21" s="0">
-        <v>0.15415578018631629</v>
+        <v>0.16557261544106208</v>
       </c>
       <c r="I21" s="0">
-        <v>0.003897091013358645</v>
+        <v>0.0098770971462846489</v>
       </c>
       <c r="J21" s="0">
-        <v>3.8394392126834496</v>
+        <v>4.7216758562058914</v>
       </c>
       <c r="K21" s="0">
-        <v>0.0087165576294649747</v>
+        <v>0.011398459637467606</v>
       </c>
       <c r="L21" s="0">
-        <v>0.0078040002901861296</v>
+        <v>0.0079470693196368961</v>
       </c>
       <c r="M21" s="0">
-        <v>0.011335733049739113</v>
+        <v>0.011681085544058917</v>
       </c>
       <c r="N21" s="0">
-        <v>0.16701524976711071</v>
+        <v>0.40876224684319912</v>
       </c>
       <c r="O21" s="0">
-        <v>0.018580289023290963</v>
+        <v>0.054453735560395428</v>
       </c>
       <c r="P21" s="0">
-        <v>0.15471977367704787</v>
+        <v>0.1059965498310854</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.0043651077542241528</v>
+        <v>0.012039140097010273</v>
       </c>
       <c r="R21" s="0">
-        <v>4.2455931965382048</v>
+        <v>5.2191501990429243</v>
       </c>
       <c r="S21" s="0">
-        <v>0.0060816021552828571</v>
+        <v>0.0069469540505856459</v>
       </c>
       <c r="T21" s="0">
-        <v>0.0082032275505418278</v>
+        <v>0.008371955890381283</v>
       </c>
       <c r="U21" s="0">
-        <v>0.010223357225296843</v>
+        <v>0.0087265638608891409</v>
       </c>
       <c r="V21" s="0">
-        <v>0.15412498333677482</v>
+        <v>0.32624147168016299</v>
       </c>
       <c r="W21" s="0">
-        <v>0.022717670174944589</v>
+        <v>0.046057688821277212</v>
       </c>
       <c r="X21" s="0">
-        <v>0.15689050161869639</v>
+        <v>0.12465234372402839</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.0048679923473693388</v>
+        <v>0.0097357522043536333</v>
       </c>
       <c r="Z21" s="0">
-        <v>3.6799753705253551</v>
+        <v>4.4393217541376924</v>
       </c>
       <c r="AA21" s="0"/>
       <c r="AB21" s="0"/>
@@ -2074,28 +2074,28 @@
       </c>
       <c r="B23" s="0"/>
       <c r="C23" s="0">
-        <v>0.017453292341473949</v>
+        <v>0.017453292339919841</v>
       </c>
       <c r="D23" s="0">
-        <v>-0.00089248622465755401</v>
+        <v>-0.00090832847885269829</v>
       </c>
       <c r="E23" s="0">
-        <v>-0.00025983456417563104</v>
+        <v>-0.00028147603853436538</v>
       </c>
       <c r="F23" s="0">
-        <v>0.76921703161563626</v>
+        <v>0.76999552452172815</v>
       </c>
       <c r="G23" s="0">
-        <v>-0.021018368309738019</v>
+        <v>-0.021125769794400586</v>
       </c>
       <c r="H23" s="0">
-        <v>0.78010356277878756</v>
+        <v>0.77927890656047849</v>
       </c>
       <c r="I23" s="0">
-        <v>0.0053699786836855726</v>
+        <v>0.0053351033353169035</v>
       </c>
       <c r="J23" s="0">
-        <v>-2.5273953112572456</v>
+        <v>-2.8211022916921924</v>
       </c>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
@@ -2106,52 +2106,52 @@
       <c r="Q23" s="0"/>
       <c r="R23" s="0"/>
       <c r="S23" s="0">
-        <v>0.018523315720472333</v>
+        <v>0.018575258091286736</v>
       </c>
       <c r="T23" s="0">
-        <v>-0.00081757205272535471</v>
+        <v>-0.00082984662802308023</v>
       </c>
       <c r="U23" s="0">
-        <v>-0.00018486191702488119</v>
+        <v>-0.00020293301824068292</v>
       </c>
       <c r="V23" s="0">
-        <v>0.77126807312634249</v>
+        <v>0.77214817060623509</v>
       </c>
       <c r="W23" s="0">
-        <v>-0.020770226037740064</v>
+        <v>-0.020865619141170851</v>
       </c>
       <c r="X23" s="0">
-        <v>0.78263874344898454</v>
+        <v>0.78193526585365247</v>
       </c>
       <c r="Y23" s="0">
-        <v>0.0055625035863827547</v>
+        <v>0.0055367413303081614</v>
       </c>
       <c r="Z23" s="0">
-        <v>-2.5227183479310398</v>
+        <v>-2.8162028923771953</v>
       </c>
       <c r="AA23" s="0">
-        <v>0.016383268962475564</v>
+        <v>0.016331326588552946</v>
       </c>
       <c r="AB23" s="0">
-        <v>-0.00096740039658975332</v>
+        <v>-0.00098681032968231624</v>
       </c>
       <c r="AC23" s="0">
-        <v>-0.00033480721132638088</v>
+        <v>-0.00036001905882804785</v>
       </c>
       <c r="AD23" s="0">
-        <v>0.76716599010493003</v>
+        <v>0.76784287843722121</v>
       </c>
       <c r="AE23" s="0">
-        <v>-0.021266510581735974</v>
+        <v>-0.021385920447630321</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.77756838210859058</v>
+        <v>0.77662254726730451</v>
       </c>
       <c r="AG23" s="0">
-        <v>0.0051774537809883905</v>
+        <v>0.0051334653403256455</v>
       </c>
       <c r="AH23" s="0">
-        <v>-2.5320722745834514</v>
+        <v>-2.8260016910071895</v>
       </c>
     </row>
   </sheetData>
